--- a/torino.xlsx
+++ b/torino.xlsx
@@ -5,16 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Z-progetti-python\qr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Z-progetti-python\qr\Etichette\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D06025C-B4FB-4CAB-9F00-C45D5346049A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{568BC2B4-ADE6-4F2F-9BCB-D633F3B92104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$K$438</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
@@ -918,18 +921,12 @@
     <t>24R01614</t>
   </si>
   <si>
-    <t xml:space="preserve">TRENSENNE CORSO INGHILTERRA LATO CIV. 17 </t>
-  </si>
-  <si>
     <t>25R00193</t>
   </si>
   <si>
     <t>25R00510</t>
   </si>
   <si>
-    <t>TRENSENNE CORSO INGHILTERRA LATO CIV. 7</t>
-  </si>
-  <si>
     <t>25R01619</t>
   </si>
   <si>
@@ -2109,9 +2106,6 @@
     <t xml:space="preserve"> VIA PAOLO VERONESE ANGOLO VIA STAMPINI </t>
   </si>
   <si>
-    <t xml:space="preserve">  STRADA DEL DROSSO FRONTE CIV. 130 </t>
-  </si>
-  <si>
     <t xml:space="preserve"> CORSO ORBASSANO QUASI FRONTE CORSO SETTEMBRINI</t>
   </si>
   <si>
@@ -2128,6 +2122,15 @@
   </si>
   <si>
     <t xml:space="preserve"> CORSO LECCE LATO CIV. 52 QUASI ANGOLO VIA FABRIZI -7 METRI PRIMA DI PALO LUCE LD58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STRADA DEL DROSSO FRONTE CIV. 130 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRANSENNE CORSO INGHILTERRA LATO CIV. 17 </t>
+  </si>
+  <si>
+    <t>TRANSENNE CORSO INGHILTERRA LATO CIV. 7</t>
   </si>
 </sst>
 </file>
@@ -2230,10 +2233,10 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -2467,7 +2470,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -2517,7 +2520,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>13</v>
@@ -2550,7 +2553,7 @@
         <v>15</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>13</v>
@@ -2583,7 +2586,7 @@
         <v>15</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>13</v>
@@ -2616,7 +2619,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>13</v>
@@ -2649,7 +2652,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>13</v>
@@ -2682,7 +2685,7 @@
         <v>12</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>13</v>
@@ -2715,7 +2718,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>13</v>
@@ -2748,7 +2751,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>13</v>
@@ -2781,7 +2784,7 @@
         <v>12</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>13</v>
@@ -2814,7 +2817,7 @@
         <v>15</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>13</v>
@@ -2828,7 +2831,7 @@
       <c r="J11" s="7">
         <v>45247</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="9">
         <v>46343</v>
       </c>
     </row>
@@ -2849,13 +2852,13 @@
         <v>15</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>27</v>
@@ -2863,7 +2866,7 @@
       <c r="J12" s="7">
         <v>45986</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K12" s="9">
         <v>47082</v>
       </c>
     </row>
@@ -2884,13 +2887,13 @@
         <v>15</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>29</v>
@@ -2919,13 +2922,13 @@
         <v>15</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>30</v>
@@ -2954,7 +2957,7 @@
         <v>12</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>13</v>
@@ -2987,7 +2990,7 @@
         <v>32</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>13</v>
@@ -3020,13 +3023,13 @@
         <v>15</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>34</v>
@@ -3055,7 +3058,7 @@
         <v>12</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>13</v>
@@ -3088,7 +3091,7 @@
         <v>32</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>13</v>
@@ -3121,7 +3124,7 @@
         <v>12</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>13</v>
@@ -3133,7 +3136,7 @@
       <c r="J20" s="7">
         <v>45931</v>
       </c>
-      <c r="K20" s="8">
+      <c r="K20" s="9">
         <v>47027</v>
       </c>
     </row>
@@ -3154,7 +3157,7 @@
         <v>12</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>13</v>
@@ -3187,7 +3190,7 @@
         <v>32</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>13</v>
@@ -3220,13 +3223,13 @@
         <v>15</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>40</v>
@@ -3255,13 +3258,13 @@
         <v>15</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I24" s="5" t="s">
         <v>41</v>
@@ -3290,13 +3293,13 @@
         <v>15</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>42</v>
@@ -3325,13 +3328,13 @@
         <v>15</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>43</v>
@@ -3360,13 +3363,13 @@
         <v>15</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>44</v>
@@ -3395,13 +3398,13 @@
         <v>15</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>45</v>
@@ -3430,13 +3433,13 @@
         <v>15</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>46</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>47</v>
@@ -3465,13 +3468,13 @@
         <v>15</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>48</v>
@@ -3500,7 +3503,7 @@
         <v>15</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>13</v>
@@ -3533,7 +3536,7 @@
         <v>12</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>13</v>
@@ -3566,13 +3569,13 @@
         <v>15</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>51</v>
@@ -3601,13 +3604,13 @@
         <v>15</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I34" s="5" t="s">
         <v>52</v>
@@ -3636,13 +3639,13 @@
         <v>15</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>53</v>
@@ -3671,13 +3674,13 @@
         <v>15</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>54</v>
@@ -3706,13 +3709,13 @@
         <v>15</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I37" s="5" t="s">
         <v>55</v>
@@ -3741,13 +3744,13 @@
         <v>15</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I38" s="5" t="s">
         <v>56</v>
@@ -3776,7 +3779,7 @@
         <v>12</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>13</v>
@@ -3809,7 +3812,7 @@
         <v>32</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>13</v>
@@ -3842,13 +3845,13 @@
         <v>15</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I41" s="5" t="s">
         <v>59</v>
@@ -3877,13 +3880,13 @@
         <v>15</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I42" s="5" t="s">
         <v>60</v>
@@ -3912,13 +3915,13 @@
         <v>15</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I43" s="5" t="s">
         <v>61</v>
@@ -3947,13 +3950,13 @@
         <v>15</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I44" s="5" t="s">
         <v>62</v>
@@ -3982,7 +3985,7 @@
         <v>12</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>13</v>
@@ -4015,7 +4018,7 @@
         <v>32</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>13</v>
@@ -4048,7 +4051,7 @@
         <v>32</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>13</v>
@@ -4081,7 +4084,7 @@
         <v>66</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>13</v>
@@ -4114,7 +4117,7 @@
         <v>15</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>13</v>
@@ -4147,7 +4150,7 @@
         <v>12</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>13</v>
@@ -4180,7 +4183,7 @@
         <v>70</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G51" s="5" t="s">
         <v>13</v>
@@ -4213,7 +4216,7 @@
         <v>72</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>13</v>
@@ -4246,7 +4249,7 @@
         <v>74</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>13</v>
@@ -4279,7 +4282,7 @@
         <v>76</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>13</v>
@@ -4312,7 +4315,7 @@
         <v>78</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>13</v>
@@ -4345,7 +4348,7 @@
         <v>32</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="G56" s="5" t="s">
         <v>13</v>
@@ -4378,7 +4381,7 @@
         <v>15</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="G57" s="5" t="s">
         <v>13</v>
@@ -4411,7 +4414,7 @@
         <v>12</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>13</v>
@@ -4444,7 +4447,7 @@
         <v>83</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="G59" s="5" t="s">
         <v>13</v>
@@ -4477,7 +4480,7 @@
         <v>15</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G60" s="5" t="s">
         <v>13</v>
@@ -4510,7 +4513,7 @@
         <v>12</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>13</v>
@@ -4543,7 +4546,7 @@
         <v>19</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G62" s="5" t="s">
         <v>13</v>
@@ -4576,7 +4579,7 @@
         <v>83</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>13</v>
@@ -4609,7 +4612,7 @@
         <v>70</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G64" s="5" t="s">
         <v>13</v>
@@ -4642,7 +4645,7 @@
         <v>72</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G65" s="5" t="s">
         <v>13</v>
@@ -4675,7 +4678,7 @@
         <v>74</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G66" s="5" t="s">
         <v>13</v>
@@ -4708,7 +4711,7 @@
         <v>76</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>13</v>
@@ -4741,7 +4744,7 @@
         <v>12</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="G68" s="5" t="s">
         <v>13</v>
@@ -4774,7 +4777,7 @@
         <v>32</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="G69" s="5" t="s">
         <v>13</v>
@@ -4807,7 +4810,7 @@
         <v>12</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="G70" s="5" t="s">
         <v>46</v>
@@ -4840,7 +4843,7 @@
         <v>32</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="G71" s="5" t="s">
         <v>46</v>
@@ -4873,7 +4876,7 @@
         <v>66</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>46</v>
@@ -4906,7 +4909,7 @@
         <v>19</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="G73" s="5" t="s">
         <v>13</v>
@@ -4939,7 +4942,7 @@
         <v>83</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="G74" s="5" t="s">
         <v>13</v>
@@ -4972,7 +4975,7 @@
         <v>70</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="G75" s="5" t="s">
         <v>46</v>
@@ -5005,7 +5008,7 @@
         <v>72</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="G76" s="5" t="s">
         <v>46</v>
@@ -5038,7 +5041,7 @@
         <v>32</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>13</v>
@@ -5071,7 +5074,7 @@
         <v>66</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="G78" s="5" t="s">
         <v>13</v>
@@ -5104,7 +5107,7 @@
         <v>66</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="G79" s="5" t="s">
         <v>13</v>
@@ -5137,7 +5140,7 @@
         <v>70</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="G80" s="5" t="s">
         <v>13</v>
@@ -5170,7 +5173,7 @@
         <v>72</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="G81" s="5" t="s">
         <v>13</v>
@@ -5203,7 +5206,7 @@
         <v>74</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="G82" s="5" t="s">
         <v>13</v>
@@ -5236,7 +5239,7 @@
         <v>12</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="G83" s="5" t="s">
         <v>13</v>
@@ -5269,13 +5272,13 @@
         <v>15</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="G84" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I84" s="5" t="s">
         <v>109</v>
@@ -5304,7 +5307,7 @@
         <v>32</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="G85" s="5" t="s">
         <v>13</v>
@@ -5337,7 +5340,7 @@
         <v>66</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="G86" s="5" t="s">
         <v>13</v>
@@ -5370,7 +5373,7 @@
         <v>19</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="G87" s="5" t="s">
         <v>13</v>
@@ -5403,7 +5406,7 @@
         <v>12</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G88" s="5" t="s">
         <v>13</v>
@@ -5436,7 +5439,7 @@
         <v>32</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G89" s="5" t="s">
         <v>13</v>
@@ -5469,13 +5472,13 @@
         <v>15</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G90" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I90" s="5" t="s">
         <v>115</v>
@@ -5504,13 +5507,13 @@
         <v>15</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="G91" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I91" s="5" t="s">
         <v>116</v>
@@ -5539,7 +5542,7 @@
         <v>15</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="G92" s="5" t="s">
         <v>13</v>
@@ -5574,7 +5577,7 @@
         <v>12</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="G93" s="5" t="s">
         <v>13</v>
@@ -5607,7 +5610,7 @@
         <v>32</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="G94" s="5" t="s">
         <v>13</v>
@@ -5640,7 +5643,7 @@
         <v>66</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="G95" s="5" t="s">
         <v>13</v>
@@ -5673,7 +5676,7 @@
         <v>19</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="G96" s="5" t="s">
         <v>13</v>
@@ -5706,7 +5709,7 @@
         <v>12</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="G97" s="5" t="s">
         <v>13</v>
@@ -5739,7 +5742,7 @@
         <v>32</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="G98" s="5" t="s">
         <v>13</v>
@@ -5772,7 +5775,7 @@
         <v>66</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="G99" s="5" t="s">
         <v>13</v>
@@ -5805,7 +5808,7 @@
         <v>19</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="G100" s="5" t="s">
         <v>13</v>
@@ -5838,7 +5841,7 @@
         <v>12</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="G101" s="5" t="s">
         <v>13</v>
@@ -5871,7 +5874,7 @@
         <v>32</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="G102" s="5" t="s">
         <v>13</v>
@@ -5904,7 +5907,7 @@
         <v>66</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="G103" s="5" t="s">
         <v>13</v>
@@ -5937,7 +5940,7 @@
         <v>15</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="G104" s="5" t="s">
         <v>13</v>
@@ -5970,7 +5973,7 @@
         <v>12</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G105" s="5" t="s">
         <v>13</v>
@@ -6003,7 +6006,7 @@
         <v>32</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G106" s="5" t="s">
         <v>13</v>
@@ -6036,7 +6039,7 @@
         <v>66</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G107" s="5" t="s">
         <v>13</v>
@@ -6069,7 +6072,7 @@
         <v>12</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="G108" s="5" t="s">
         <v>28</v>
@@ -6102,7 +6105,7 @@
         <v>32</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="G109" s="5" t="s">
         <v>28</v>
@@ -6135,7 +6138,7 @@
         <v>12</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="G110" s="5" t="s">
         <v>28</v>
@@ -6168,7 +6171,7 @@
         <v>32</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="G111" s="5" t="s">
         <v>28</v>
@@ -6201,7 +6204,7 @@
         <v>66</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="G112" s="5" t="s">
         <v>28</v>
@@ -6234,7 +6237,7 @@
         <v>19</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="G113" s="5" t="s">
         <v>28</v>
@@ -6267,7 +6270,7 @@
         <v>12</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="G114" s="5" t="s">
         <v>28</v>
@@ -6300,7 +6303,7 @@
         <v>32</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="G115" s="5" t="s">
         <v>28</v>
@@ -6333,7 +6336,7 @@
         <v>66</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="G116" s="5" t="s">
         <v>28</v>
@@ -6366,7 +6369,7 @@
         <v>12</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="G117" s="5" t="s">
         <v>28</v>
@@ -6399,7 +6402,7 @@
         <v>32</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="G118" s="5" t="s">
         <v>28</v>
@@ -6432,7 +6435,7 @@
         <v>12</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="G119" s="5" t="s">
         <v>28</v>
@@ -6465,7 +6468,7 @@
         <v>32</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="G120" s="5" t="s">
         <v>28</v>
@@ -6498,7 +6501,7 @@
         <v>32</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G121" s="5" t="s">
         <v>28</v>
@@ -6531,7 +6534,7 @@
         <v>66</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G122" s="5" t="s">
         <v>28</v>
@@ -6564,7 +6567,7 @@
         <v>19</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G123" s="5" t="s">
         <v>28</v>
@@ -6597,7 +6600,7 @@
         <v>83</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G124" s="5" t="s">
         <v>149</v>
@@ -6630,7 +6633,7 @@
         <v>70</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G125" s="5" t="s">
         <v>28</v>
@@ -6663,7 +6666,7 @@
         <v>72</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G126" s="5" t="s">
         <v>28</v>
@@ -6696,7 +6699,7 @@
         <v>15</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="G127" s="5" t="s">
         <v>13</v>
@@ -6729,7 +6732,7 @@
         <v>15</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="G128" s="5" t="s">
         <v>13</v>
@@ -6764,7 +6767,7 @@
         <v>12</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="G129" s="5" t="s">
         <v>13</v>
@@ -6797,7 +6800,7 @@
         <v>32</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="G130" s="5" t="s">
         <v>13</v>
@@ -6830,7 +6833,7 @@
         <v>19</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="G131" s="5" t="s">
         <v>13</v>
@@ -6863,7 +6866,7 @@
         <v>83</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="G132" s="5" t="s">
         <v>13</v>
@@ -6896,7 +6899,7 @@
         <v>15</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="G133" s="5" t="s">
         <v>13</v>
@@ -6929,7 +6932,7 @@
         <v>32</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="G134" s="5" t="s">
         <v>13</v>
@@ -6962,7 +6965,7 @@
         <v>12</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="G135" s="5" t="s">
         <v>13</v>
@@ -6995,7 +6998,7 @@
         <v>12</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="G136" s="5" t="s">
         <v>13</v>
@@ -7028,7 +7031,7 @@
         <v>15</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="G137" s="5" t="s">
         <v>13</v>
@@ -7061,7 +7064,7 @@
         <v>32</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="G138" s="5" t="s">
         <v>13</v>
@@ -7094,7 +7097,7 @@
         <v>12</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G139" s="5" t="s">
         <v>13</v>
@@ -7127,7 +7130,7 @@
         <v>32</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G140" s="5" t="s">
         <v>13</v>
@@ -7160,7 +7163,7 @@
         <v>12</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="G141" s="5" t="s">
         <v>13</v>
@@ -7193,7 +7196,7 @@
         <v>15</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="G142" s="5" t="s">
         <v>168</v>
@@ -7226,7 +7229,7 @@
         <v>32</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G143" s="5" t="s">
         <v>13</v>
@@ -7259,7 +7262,7 @@
         <v>66</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G144" s="5" t="s">
         <v>13</v>
@@ -7292,7 +7295,7 @@
         <v>19</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G145" s="5" t="s">
         <v>13</v>
@@ -7325,7 +7328,7 @@
         <v>15</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G146" s="5" t="s">
         <v>13</v>
@@ -7358,7 +7361,7 @@
         <v>12</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G147" s="5" t="s">
         <v>13</v>
@@ -7391,7 +7394,7 @@
         <v>19</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G148" s="5" t="s">
         <v>13</v>
@@ -7424,7 +7427,7 @@
         <v>72</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G149" s="5" t="s">
         <v>13</v>
@@ -7457,7 +7460,7 @@
         <v>32</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G150" s="5" t="s">
         <v>13</v>
@@ -7490,7 +7493,7 @@
         <v>66</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G151" s="5" t="s">
         <v>13</v>
@@ -7523,7 +7526,7 @@
         <v>19</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G152" s="5" t="s">
         <v>13</v>
@@ -7556,7 +7559,7 @@
         <v>12</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="G153" s="5" t="s">
         <v>13</v>
@@ -7589,7 +7592,7 @@
         <v>32</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="G154" s="5" t="s">
         <v>13</v>
@@ -7622,7 +7625,7 @@
         <v>66</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="G155" s="5" t="s">
         <v>13</v>
@@ -7655,7 +7658,7 @@
         <v>12</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="G156" s="5" t="s">
         <v>13</v>
@@ -7688,7 +7691,7 @@
         <v>32</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="G157" s="5" t="s">
         <v>13</v>
@@ -7721,7 +7724,7 @@
         <v>66</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="G158" s="5" t="s">
         <v>13</v>
@@ -7754,7 +7757,7 @@
         <v>12</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="G159" s="5" t="s">
         <v>13</v>
@@ -7787,7 +7790,7 @@
         <v>15</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="G160" s="5" t="s">
         <v>13</v>
@@ -7822,7 +7825,7 @@
         <v>15</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="G161" s="5" t="s">
         <v>46</v>
@@ -7857,7 +7860,7 @@
         <v>15</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="G162" s="5" t="s">
         <v>13</v>
@@ -7892,13 +7895,13 @@
         <v>15</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G163" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H163" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I163" s="5" t="s">
         <v>190</v>
@@ -7927,13 +7930,13 @@
         <v>15</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="G164" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H164" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I164" s="5" t="s">
         <v>191</v>
@@ -7962,13 +7965,13 @@
         <v>15</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G165" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H165" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I165" s="5" t="s">
         <v>192</v>
@@ -7997,7 +8000,7 @@
         <v>15</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="G166" s="5" t="s">
         <v>13</v>
@@ -8032,7 +8035,7 @@
         <v>15</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="G167" s="5" t="s">
         <v>13</v>
@@ -8067,7 +8070,7 @@
         <v>15</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G168" s="5" t="s">
         <v>13</v>
@@ -8102,7 +8105,7 @@
         <v>15</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="G169" s="5" t="s">
         <v>13</v>
@@ -8137,7 +8140,7 @@
         <v>15</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G170" s="5" t="s">
         <v>13</v>
@@ -8172,7 +8175,7 @@
         <v>15</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="G171" s="5" t="s">
         <v>13</v>
@@ -8207,7 +8210,7 @@
         <v>15</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="G172" s="5" t="s">
         <v>13</v>
@@ -8242,7 +8245,7 @@
         <v>15</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="G173" s="5" t="s">
         <v>13</v>
@@ -8277,7 +8280,7 @@
         <v>15</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="G174" s="5" t="s">
         <v>13</v>
@@ -8312,7 +8315,7 @@
         <v>15</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="G175" s="5" t="s">
         <v>13</v>
@@ -8347,7 +8350,7 @@
         <v>15</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="G176" s="5" t="s">
         <v>13</v>
@@ -8382,7 +8385,7 @@
         <v>15</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="G177" s="5" t="s">
         <v>13</v>
@@ -8417,7 +8420,7 @@
         <v>15</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="G178" s="5" t="s">
         <v>13</v>
@@ -8452,7 +8455,7 @@
         <v>15</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="G179" s="5" t="s">
         <v>13</v>
@@ -8487,7 +8490,7 @@
         <v>15</v>
       </c>
       <c r="F180" s="5" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="G180" s="5" t="s">
         <v>13</v>
@@ -8522,7 +8525,7 @@
         <v>15</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="G181" s="5" t="s">
         <v>13</v>
@@ -8557,7 +8560,7 @@
         <v>15</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="G182" s="5" t="s">
         <v>13</v>
@@ -8592,7 +8595,7 @@
         <v>15</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="G183" s="5" t="s">
         <v>13</v>
@@ -8627,7 +8630,7 @@
         <v>12</v>
       </c>
       <c r="F184" s="5" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="G184" s="5" t="s">
         <v>13</v>
@@ -8660,7 +8663,7 @@
         <v>12</v>
       </c>
       <c r="F185" s="5" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="G185" s="5" t="s">
         <v>13</v>
@@ -8693,7 +8696,7 @@
         <v>12</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="G186" s="5" t="s">
         <v>13</v>
@@ -8726,7 +8729,7 @@
         <v>12</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="G187" s="5" t="s">
         <v>13</v>
@@ -8759,7 +8762,7 @@
         <v>32</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G188" s="5" t="s">
         <v>13</v>
@@ -8792,7 +8795,7 @@
         <v>66</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G189" s="5" t="s">
         <v>13</v>
@@ -8825,7 +8828,7 @@
         <v>19</v>
       </c>
       <c r="F190" s="5" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G190" s="5" t="s">
         <v>13</v>
@@ -8858,7 +8861,7 @@
         <v>70</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G191" s="5" t="s">
         <v>13</v>
@@ -8891,7 +8894,7 @@
         <v>12</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="G192" s="5" t="s">
         <v>13</v>
@@ -8924,7 +8927,7 @@
         <v>32</v>
       </c>
       <c r="F193" s="5" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="G193" s="5" t="s">
         <v>13</v>
@@ -8957,7 +8960,7 @@
         <v>19</v>
       </c>
       <c r="F194" s="5" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="G194" s="5" t="s">
         <v>221</v>
@@ -8990,7 +8993,7 @@
         <v>12</v>
       </c>
       <c r="F195" s="5" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G195" s="5" t="s">
         <v>13</v>
@@ -9023,7 +9026,7 @@
         <v>32</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G196" s="5" t="s">
         <v>13</v>
@@ -9056,7 +9059,7 @@
         <v>66</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G197" s="5" t="s">
         <v>13</v>
@@ -9089,7 +9092,7 @@
         <v>32</v>
       </c>
       <c r="F198" s="5" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G198" s="5" t="s">
         <v>13</v>
@@ -9122,7 +9125,7 @@
         <v>66</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G199" s="5" t="s">
         <v>13</v>
@@ -9155,7 +9158,7 @@
         <v>19</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G200" s="5" t="s">
         <v>13</v>
@@ -9188,7 +9191,7 @@
         <v>12</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="G201" s="5" t="s">
         <v>13</v>
@@ -9221,7 +9224,7 @@
         <v>32</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="G202" s="5" t="s">
         <v>13</v>
@@ -9254,7 +9257,7 @@
         <v>12</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="G203" s="5" t="s">
         <v>13</v>
@@ -9287,7 +9290,7 @@
         <v>66</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="G204" s="5" t="s">
         <v>13</v>
@@ -9320,7 +9323,7 @@
         <v>70</v>
       </c>
       <c r="F205" s="5" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="G205" s="5" t="s">
         <v>13</v>
@@ -9353,7 +9356,7 @@
         <v>72</v>
       </c>
       <c r="F206" s="5" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="G206" s="5" t="s">
         <v>13</v>
@@ -9386,7 +9389,7 @@
         <v>74</v>
       </c>
       <c r="F207" s="5" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="G207" s="5" t="s">
         <v>13</v>
@@ -9419,7 +9422,7 @@
         <v>78</v>
       </c>
       <c r="F208" s="5" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="G208" s="5" t="s">
         <v>13</v>
@@ -9452,7 +9455,7 @@
         <v>12</v>
       </c>
       <c r="F209" s="5" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="G209" s="5" t="s">
         <v>13</v>
@@ -9485,7 +9488,7 @@
         <v>32</v>
       </c>
       <c r="F210" s="5" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="G210" s="5" t="s">
         <v>13</v>
@@ -9518,7 +9521,7 @@
         <v>66</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="G211" s="5" t="s">
         <v>13</v>
@@ -9551,7 +9554,7 @@
         <v>12</v>
       </c>
       <c r="F212" s="5" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="G212" s="5" t="s">
         <v>13</v>
@@ -9584,7 +9587,7 @@
         <v>32</v>
       </c>
       <c r="F213" s="5" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="G213" s="5" t="s">
         <v>13</v>
@@ -9617,13 +9620,13 @@
         <v>15</v>
       </c>
       <c r="F214" s="5" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="G214" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H214" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I214" s="5" t="s">
         <v>242</v>
@@ -9652,7 +9655,7 @@
         <v>15</v>
       </c>
       <c r="F215" s="5" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="G215" s="5" t="s">
         <v>13</v>
@@ -9687,7 +9690,7 @@
         <v>15</v>
       </c>
       <c r="F216" s="5" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G216" s="5" t="s">
         <v>13</v>
@@ -9722,7 +9725,7 @@
         <v>12</v>
       </c>
       <c r="F217" s="5" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="G217" s="5" t="s">
         <v>13</v>
@@ -9755,7 +9758,7 @@
         <v>32</v>
       </c>
       <c r="F218" s="5" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="G218" s="5" t="s">
         <v>13</v>
@@ -9788,7 +9791,7 @@
         <v>15</v>
       </c>
       <c r="F219" s="5" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="G219" s="5" t="s">
         <v>13</v>
@@ -9823,13 +9826,13 @@
         <v>15</v>
       </c>
       <c r="F220" s="5" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="G220" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H220" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I220" s="5" t="s">
         <v>248</v>
@@ -9858,7 +9861,7 @@
         <v>12</v>
       </c>
       <c r="F221" s="5" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="G221" s="5" t="s">
         <v>13</v>
@@ -9891,7 +9894,7 @@
         <v>32</v>
       </c>
       <c r="F222" s="5" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="G222" s="5" t="s">
         <v>13</v>
@@ -9924,7 +9927,7 @@
         <v>66</v>
       </c>
       <c r="F223" s="5" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="G223" s="5" t="s">
         <v>13</v>
@@ -9957,7 +9960,7 @@
         <v>66</v>
       </c>
       <c r="F224" s="5" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G224" s="5" t="s">
         <v>13</v>
@@ -9990,7 +9993,7 @@
         <v>19</v>
       </c>
       <c r="F225" s="5" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G225" s="5" t="s">
         <v>13</v>
@@ -10023,7 +10026,7 @@
         <v>83</v>
       </c>
       <c r="F226" s="5" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G226" s="5" t="s">
         <v>13</v>
@@ -10056,7 +10059,7 @@
         <v>70</v>
       </c>
       <c r="F227" s="5" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G227" s="5" t="s">
         <v>13</v>
@@ -10089,7 +10092,7 @@
         <v>72</v>
       </c>
       <c r="F228" s="5" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G228" s="5" t="s">
         <v>13</v>
@@ -10122,7 +10125,7 @@
         <v>74</v>
       </c>
       <c r="F229" s="5" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G229" s="5" t="s">
         <v>13</v>
@@ -10155,7 +10158,7 @@
         <v>76</v>
       </c>
       <c r="F230" s="5" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G230" s="5" t="s">
         <v>13</v>
@@ -10188,7 +10191,7 @@
         <v>32</v>
       </c>
       <c r="F231" s="5" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="G231" s="5" t="s">
         <v>13</v>
@@ -10221,7 +10224,7 @@
         <v>66</v>
       </c>
       <c r="F232" s="5" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="G232" s="5" t="s">
         <v>13</v>
@@ -10254,7 +10257,7 @@
         <v>19</v>
       </c>
       <c r="F233" s="5" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="G233" s="5" t="s">
         <v>13</v>
@@ -10287,7 +10290,7 @@
         <v>83</v>
       </c>
       <c r="F234" s="5" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="G234" s="5" t="s">
         <v>13</v>
@@ -10320,7 +10323,7 @@
         <v>70</v>
       </c>
       <c r="F235" s="5" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="G235" s="5" t="s">
         <v>13</v>
@@ -10353,7 +10356,7 @@
         <v>12</v>
       </c>
       <c r="F236" s="5" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="G236" s="5" t="s">
         <v>13</v>
@@ -10386,7 +10389,7 @@
         <v>32</v>
       </c>
       <c r="F237" s="5" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="G237" s="5" t="s">
         <v>13</v>
@@ -10419,7 +10422,7 @@
         <v>66</v>
       </c>
       <c r="F238" s="5" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="G238" s="5" t="s">
         <v>13</v>
@@ -10452,7 +10455,7 @@
         <v>15</v>
       </c>
       <c r="F239" s="5" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="G239" s="5" t="s">
         <v>13</v>
@@ -10487,7 +10490,7 @@
         <v>15</v>
       </c>
       <c r="F240" s="5" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="G240" s="5" t="s">
         <v>13</v>
@@ -10522,7 +10525,7 @@
         <v>32</v>
       </c>
       <c r="F241" s="5" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="G241" s="5" t="s">
         <v>13</v>
@@ -10555,7 +10558,7 @@
         <v>66</v>
       </c>
       <c r="F242" s="5" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="G242" s="5" t="s">
         <v>13</v>
@@ -10588,7 +10591,7 @@
         <v>19</v>
       </c>
       <c r="F243" s="5" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="G243" s="5" t="s">
         <v>13</v>
@@ -10621,7 +10624,7 @@
         <v>83</v>
       </c>
       <c r="F244" s="5" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="G244" s="5" t="s">
         <v>13</v>
@@ -10654,7 +10657,7 @@
         <v>70</v>
       </c>
       <c r="F245" s="5" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="G245" s="5" t="s">
         <v>13</v>
@@ -10687,7 +10690,7 @@
         <v>72</v>
       </c>
       <c r="F246" s="5" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="G246" s="5" t="s">
         <v>13</v>
@@ -10720,7 +10723,7 @@
         <v>74</v>
       </c>
       <c r="F247" s="5" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="G247" s="5" t="s">
         <v>13</v>
@@ -10753,7 +10756,7 @@
         <v>76</v>
       </c>
       <c r="F248" s="5" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="G248" s="5" t="s">
         <v>13</v>
@@ -10786,13 +10789,13 @@
         <v>15</v>
       </c>
       <c r="F249" s="5" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G249" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H249" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I249" s="5" t="s">
         <v>277</v>
@@ -10827,7 +10830,7 @@
         <v>13</v>
       </c>
       <c r="H250" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I250" s="5" t="s">
         <v>279</v>
@@ -10856,7 +10859,7 @@
         <v>12</v>
       </c>
       <c r="F251" s="5" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="G251" s="5" t="s">
         <v>13</v>
@@ -10889,7 +10892,7 @@
         <v>32</v>
       </c>
       <c r="F252" s="5" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="G252" s="5" t="s">
         <v>13</v>
@@ -10922,7 +10925,7 @@
         <v>66</v>
       </c>
       <c r="F253" s="5" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="G253" s="5" t="s">
         <v>13</v>
@@ -10961,7 +10964,7 @@
         <v>13</v>
       </c>
       <c r="H254" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I254" s="5" t="s">
         <v>284</v>
@@ -10990,7 +10993,7 @@
         <v>15</v>
       </c>
       <c r="F255" s="5" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="G255" s="5" t="s">
         <v>13</v>
@@ -11025,7 +11028,7 @@
         <v>32</v>
       </c>
       <c r="F256" s="5" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="G256" s="5" t="s">
         <v>13</v>
@@ -11058,7 +11061,7 @@
         <v>66</v>
       </c>
       <c r="F257" s="5" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="G257" s="5" t="s">
         <v>13</v>
@@ -11091,7 +11094,7 @@
         <v>19</v>
       </c>
       <c r="F258" s="5" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="G258" s="5" t="s">
         <v>13</v>
@@ -11124,7 +11127,7 @@
         <v>83</v>
       </c>
       <c r="F259" s="5" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="G259" s="5" t="s">
         <v>13</v>
@@ -11157,7 +11160,7 @@
         <v>70</v>
       </c>
       <c r="F260" s="5" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="G260" s="5" t="s">
         <v>13</v>
@@ -11190,7 +11193,7 @@
         <v>15</v>
       </c>
       <c r="F261" s="5" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="G261" s="5" t="s">
         <v>13</v>
@@ -11225,13 +11228,13 @@
         <v>15</v>
       </c>
       <c r="F262" s="5" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="G262" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H262" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I262" s="5" t="s">
         <v>292</v>
@@ -11260,13 +11263,13 @@
         <v>15</v>
       </c>
       <c r="F263" s="5" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="G263" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H263" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I263" s="5" t="s">
         <v>293</v>
@@ -11295,13 +11298,13 @@
         <v>15</v>
       </c>
       <c r="F264" s="5" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="G264" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H264" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I264" s="5" t="s">
         <v>294</v>
@@ -11330,13 +11333,13 @@
         <v>15</v>
       </c>
       <c r="F265" s="5" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="G265" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H265" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I265" s="5" t="s">
         <v>295</v>
@@ -11365,13 +11368,13 @@
         <v>15</v>
       </c>
       <c r="F266" s="5" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="G266" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H266" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I266" s="5" t="s">
         <v>296</v>
@@ -11400,14 +11403,14 @@
         <v>15</v>
       </c>
       <c r="F267" s="5" t="s">
-        <v>297</v>
+        <v>699</v>
       </c>
       <c r="G267" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H267" s="5"/>
       <c r="I267" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J267" s="7">
         <v>45705</v>
@@ -11433,14 +11436,14 @@
         <v>12</v>
       </c>
       <c r="F268" s="5" t="s">
-        <v>297</v>
+        <v>699</v>
       </c>
       <c r="G268" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H268" s="5"/>
       <c r="I268" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J268" s="7">
         <v>45758</v>
@@ -11466,14 +11469,14 @@
         <v>15</v>
       </c>
       <c r="F269" s="5" t="s">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="G269" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H269" s="5"/>
       <c r="I269" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J269" s="7">
         <v>45953</v>
@@ -11499,14 +11502,14 @@
         <v>12</v>
       </c>
       <c r="F270" s="5" t="s">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="G270" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H270" s="5"/>
       <c r="I270" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="J270" s="7">
         <v>45705</v>
@@ -11532,14 +11535,14 @@
         <v>12</v>
       </c>
       <c r="F271" s="5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="G271" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H271" s="5"/>
       <c r="I271" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="J271" s="7">
         <v>46008</v>
@@ -11565,14 +11568,14 @@
         <v>32</v>
       </c>
       <c r="F272" s="5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="G272" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H272" s="5"/>
       <c r="I272" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="J272" s="7">
         <v>46008</v>
@@ -11598,14 +11601,14 @@
         <v>66</v>
       </c>
       <c r="F273" s="5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="G273" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H273" s="5"/>
       <c r="I273" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J273" s="7">
         <v>46008</v>
@@ -11631,14 +11634,14 @@
         <v>19</v>
       </c>
       <c r="F274" s="5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="G274" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H274" s="5"/>
       <c r="I274" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J274" s="7">
         <v>46008</v>
@@ -11664,16 +11667,16 @@
         <v>15</v>
       </c>
       <c r="F275" s="5" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="G275" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H275" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I275" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="J275" s="7">
         <v>45615</v>
@@ -11699,16 +11702,16 @@
         <v>15</v>
       </c>
       <c r="F276" s="5" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="G276" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H276" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I276" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="J276" s="7">
         <v>45531</v>
@@ -11734,16 +11737,16 @@
         <v>15</v>
       </c>
       <c r="F277" s="5" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="G277" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H277" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I277" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J277" s="7">
         <v>45531</v>
@@ -11769,16 +11772,16 @@
         <v>15</v>
       </c>
       <c r="F278" s="5" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="G278" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H278" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I278" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J278" s="7">
         <v>45247</v>
@@ -11804,16 +11807,16 @@
         <v>15</v>
       </c>
       <c r="F279" s="5" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="G279" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H279" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I279" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="J279" s="7">
         <v>45377</v>
@@ -11839,14 +11842,14 @@
         <v>12</v>
       </c>
       <c r="F280" s="5" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="G280" s="5" t="s">
         <v>46</v>
       </c>
       <c r="H280" s="5"/>
       <c r="I280" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="J280" s="7">
         <v>44636</v>
@@ -11872,14 +11875,14 @@
         <v>19</v>
       </c>
       <c r="F281" s="5" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="G281" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H281" s="5"/>
       <c r="I281" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="J281" s="7">
         <v>45730</v>
@@ -11905,14 +11908,14 @@
         <v>70</v>
       </c>
       <c r="F282" s="5" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="G282" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H282" s="5"/>
       <c r="I282" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="J282" s="7">
         <v>45531</v>
@@ -11938,14 +11941,14 @@
         <v>74</v>
       </c>
       <c r="F283" s="5" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="G283" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H283" s="5"/>
       <c r="I283" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="J283" s="7">
         <v>45730</v>
@@ -11971,16 +11974,16 @@
         <v>15</v>
       </c>
       <c r="F284" s="5" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="G284" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H284" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I284" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J284" s="7">
         <v>44995</v>
@@ -12006,16 +12009,16 @@
         <v>15</v>
       </c>
       <c r="F285" s="5" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="G285" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H285" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I285" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="J285" s="7">
         <v>44995</v>
@@ -12041,14 +12044,14 @@
         <v>32</v>
       </c>
       <c r="F286" s="5" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="G286" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H286" s="5"/>
       <c r="I286" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="J286" s="7">
         <v>45796</v>
@@ -12074,14 +12077,14 @@
         <v>19</v>
       </c>
       <c r="F287" s="5" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="G287" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H287" s="5"/>
       <c r="I287" s="5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J287" s="7">
         <v>45799</v>
@@ -12107,14 +12110,14 @@
         <v>12</v>
       </c>
       <c r="F288" s="5" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="G288" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H288" s="5"/>
       <c r="I288" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J288" s="7">
         <v>45974</v>
@@ -12140,14 +12143,14 @@
         <v>32</v>
       </c>
       <c r="F289" s="5" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="G289" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H289" s="5"/>
       <c r="I289" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J289" s="7">
         <v>45974</v>
@@ -12173,14 +12176,14 @@
         <v>66</v>
       </c>
       <c r="F290" s="5" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="G290" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H290" s="5"/>
       <c r="I290" s="5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="J290" s="7">
         <v>45974</v>
@@ -12206,16 +12209,16 @@
         <v>15</v>
       </c>
       <c r="F291" s="5" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="G291" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H291" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I291" s="5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="J291" s="7">
         <v>45064</v>
@@ -12241,16 +12244,16 @@
         <v>15</v>
       </c>
       <c r="F292" s="5" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="G292" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H292" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I292" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J292" s="7">
         <v>45615</v>
@@ -12276,14 +12279,14 @@
         <v>32</v>
       </c>
       <c r="F293" s="5" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="G293" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H293" s="5"/>
       <c r="I293" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="J293" s="7">
         <v>45394</v>
@@ -12309,14 +12312,14 @@
         <v>66</v>
       </c>
       <c r="F294" s="5" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="G294" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H294" s="5"/>
       <c r="I294" s="5" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="J294" s="7">
         <v>45615</v>
@@ -12342,14 +12345,14 @@
         <v>12</v>
       </c>
       <c r="F295" s="5" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="G295" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H295" s="5"/>
       <c r="I295" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="J295" s="7">
         <v>45869</v>
@@ -12375,14 +12378,14 @@
         <v>32</v>
       </c>
       <c r="F296" s="5" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="G296" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H296" s="5"/>
       <c r="I296" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="J296" s="7">
         <v>45869</v>
@@ -12408,14 +12411,14 @@
         <v>66</v>
       </c>
       <c r="F297" s="5" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="G297" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H297" s="5"/>
       <c r="I297" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="J297" s="7">
         <v>45869</v>
@@ -12441,14 +12444,14 @@
         <v>12</v>
       </c>
       <c r="F298" s="5" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="G298" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H298" s="5"/>
       <c r="I298" s="5" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="J298" s="7">
         <v>45905</v>
@@ -12474,14 +12477,14 @@
         <v>32</v>
       </c>
       <c r="F299" s="5" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="G299" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H299" s="5"/>
       <c r="I299" s="5" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="J299" s="7">
         <v>45905</v>
@@ -12507,14 +12510,14 @@
         <v>12</v>
       </c>
       <c r="F300" s="5" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="G300" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H300" s="5"/>
       <c r="I300" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="J300" s="7">
         <v>45931</v>
@@ -12540,14 +12543,14 @@
         <v>32</v>
       </c>
       <c r="F301" s="5" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="G301" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H301" s="5"/>
       <c r="I301" s="5" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="J301" s="7">
         <v>45931</v>
@@ -12573,14 +12576,14 @@
         <v>66</v>
       </c>
       <c r="F302" s="5" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="G302" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H302" s="5"/>
       <c r="I302" s="5" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="J302" s="7">
         <v>45931</v>
@@ -12606,14 +12609,14 @@
         <v>32</v>
       </c>
       <c r="F303" s="5" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="G303" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H303" s="5"/>
       <c r="I303" s="5" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J303" s="7">
         <v>44984</v>
@@ -12639,14 +12642,14 @@
         <v>66</v>
       </c>
       <c r="F304" s="5" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="G304" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H304" s="5"/>
       <c r="I304" s="5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="J304" s="7">
         <v>44985</v>
@@ -12672,14 +12675,14 @@
         <v>66</v>
       </c>
       <c r="F305" s="5" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="G305" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H305" s="5"/>
       <c r="I305" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="J305" s="7">
         <v>44985</v>
@@ -12705,14 +12708,14 @@
         <v>12</v>
       </c>
       <c r="F306" s="5" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="G306" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H306" s="5"/>
       <c r="I306" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="J306" s="7">
         <v>44984</v>
@@ -12738,14 +12741,14 @@
         <v>32</v>
       </c>
       <c r="F307" s="5" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="G307" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H307" s="5"/>
       <c r="I307" s="5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="J307" s="7">
         <v>44985</v>
@@ -12771,14 +12774,14 @@
         <v>66</v>
       </c>
       <c r="F308" s="5" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="G308" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H308" s="5"/>
       <c r="I308" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="J308" s="7">
         <v>44984</v>
@@ -12804,14 +12807,14 @@
         <v>19</v>
       </c>
       <c r="F309" s="5" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="G309" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H309" s="5"/>
       <c r="I309" s="5" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="J309" s="7">
         <v>44984</v>
@@ -12837,14 +12840,14 @@
         <v>32</v>
       </c>
       <c r="F310" s="5" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G310" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H310" s="5"/>
       <c r="I310" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="J310" s="7">
         <v>44985</v>
@@ -12870,14 +12873,14 @@
         <v>66</v>
       </c>
       <c r="F311" s="5" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G311" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H311" s="5"/>
       <c r="I311" s="5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="J311" s="7">
         <v>44985</v>
@@ -12903,14 +12906,14 @@
         <v>19</v>
       </c>
       <c r="F312" s="5" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G312" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H312" s="5"/>
       <c r="I312" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="J312" s="7">
         <v>44984</v>
@@ -12936,14 +12939,14 @@
         <v>83</v>
       </c>
       <c r="F313" s="5" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G313" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H313" s="5"/>
       <c r="I313" s="5" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="J313" s="7">
         <v>44988</v>
@@ -12969,14 +12972,14 @@
         <v>32</v>
       </c>
       <c r="F314" s="5" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="G314" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H314" s="5"/>
       <c r="I314" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="J314" s="7">
         <v>45869</v>
@@ -13002,14 +13005,14 @@
         <v>66</v>
       </c>
       <c r="F315" s="5" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="G315" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H315" s="5"/>
       <c r="I315" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="J315" s="7">
         <v>45869</v>
@@ -13035,14 +13038,14 @@
         <v>19</v>
       </c>
       <c r="F316" s="5" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="G316" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H316" s="5"/>
       <c r="I316" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="J316" s="7">
         <v>45869</v>
@@ -13068,14 +13071,14 @@
         <v>12</v>
       </c>
       <c r="F317" s="5" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="G317" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H317" s="5"/>
       <c r="I317" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="J317" s="7">
         <v>44988</v>
@@ -13101,14 +13104,14 @@
         <v>32</v>
       </c>
       <c r="F318" s="5" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="G318" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H318" s="5"/>
       <c r="I318" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="J318" s="7">
         <v>44988</v>
@@ -13134,14 +13137,14 @@
         <v>66</v>
       </c>
       <c r="F319" s="5" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="G319" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H319" s="5"/>
       <c r="I319" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="J319" s="7">
         <v>44984</v>
@@ -13167,14 +13170,14 @@
         <v>19</v>
       </c>
       <c r="F320" s="5" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="G320" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H320" s="5"/>
       <c r="I320" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="J320" s="7">
         <v>44984</v>
@@ -13200,16 +13203,16 @@
         <v>15</v>
       </c>
       <c r="F321" s="5" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="G321" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H321" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I321" s="5" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="J321" s="7">
         <v>45965</v>
@@ -13235,16 +13238,16 @@
         <v>15</v>
       </c>
       <c r="F322" s="5" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="G322" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H322" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I322" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="J322" s="7">
         <v>45505</v>
@@ -13270,14 +13273,14 @@
         <v>12</v>
       </c>
       <c r="F323" s="5" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="G323" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H323" s="5"/>
       <c r="I323" s="5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J323" s="7">
         <v>45280</v>
@@ -13303,14 +13306,14 @@
         <v>32</v>
       </c>
       <c r="F324" s="5" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="G324" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H324" s="5"/>
       <c r="I324" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="J324" s="7">
         <v>45265</v>
@@ -13336,16 +13339,16 @@
         <v>15</v>
       </c>
       <c r="F325" s="5" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="G325" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H325" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I325" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J325" s="7">
         <v>45615</v>
@@ -13371,16 +13374,16 @@
         <v>15</v>
       </c>
       <c r="F326" s="5" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="G326" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H326" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I326" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="J326" s="7">
         <v>45607</v>
@@ -13406,16 +13409,16 @@
         <v>15</v>
       </c>
       <c r="F327" s="5" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="G327" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H327" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I327" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="J327" s="7">
         <v>45615</v>
@@ -13441,16 +13444,16 @@
         <v>15</v>
       </c>
       <c r="F328" s="5" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="G328" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H328" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I328" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J328" s="7">
         <v>44217</v>
@@ -13476,16 +13479,16 @@
         <v>15</v>
       </c>
       <c r="F329" s="5" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G329" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H329" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I329" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J329" s="7">
         <v>45114</v>
@@ -13511,16 +13514,16 @@
         <v>15</v>
       </c>
       <c r="F330" s="5" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="G330" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H330" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I330" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J330" s="7">
         <v>45607</v>
@@ -13546,16 +13549,16 @@
         <v>15</v>
       </c>
       <c r="F331" s="5" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="G331" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H331" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I331" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J331" s="7">
         <v>45607</v>
@@ -13581,16 +13584,16 @@
         <v>15</v>
       </c>
       <c r="F332" s="5" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G332" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H332" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I332" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="J332" s="7">
         <v>45394</v>
@@ -13616,16 +13619,16 @@
         <v>15</v>
       </c>
       <c r="F333" s="5" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="G333" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H333" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I333" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="J333" s="7">
         <v>45531</v>
@@ -13651,16 +13654,16 @@
         <v>15</v>
       </c>
       <c r="F334" s="5" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G334" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H334" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I334" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="J334" s="7">
         <v>45394</v>
@@ -13686,16 +13689,16 @@
         <v>15</v>
       </c>
       <c r="F335" s="5" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G335" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H335" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I335" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="J335" s="7">
         <v>45394</v>
@@ -13721,16 +13724,16 @@
         <v>15</v>
       </c>
       <c r="F336" s="5" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G336" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H336" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I336" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="J336" s="7">
         <v>45531</v>
@@ -13756,16 +13759,16 @@
         <v>15</v>
       </c>
       <c r="F337" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="G337" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H337" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I337" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="J337" s="7">
         <v>45615</v>
@@ -13791,16 +13794,16 @@
         <v>15</v>
       </c>
       <c r="F338" s="5" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G338" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H338" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I338" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="J338" s="7">
         <v>45615</v>
@@ -13826,16 +13829,16 @@
         <v>15</v>
       </c>
       <c r="F339" s="5" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="G339" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H339" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I339" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="J339" s="7">
         <v>45531</v>
@@ -13861,14 +13864,14 @@
         <v>12</v>
       </c>
       <c r="F340" s="5" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="G340" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H340" s="5"/>
       <c r="I340" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="J340" s="7">
         <v>45607</v>
@@ -13894,14 +13897,14 @@
         <v>32</v>
       </c>
       <c r="F341" s="5" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="G341" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H341" s="5"/>
       <c r="I341" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="J341" s="7">
         <v>45607</v>
@@ -13927,16 +13930,16 @@
         <v>15</v>
       </c>
       <c r="F342" s="5" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G342" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H342" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I342" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="J342" s="7">
         <v>45828</v>
@@ -13962,16 +13965,16 @@
         <v>15</v>
       </c>
       <c r="F343" s="5" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="G343" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H343" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I343" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="J343" s="7">
         <v>45758</v>
@@ -13997,16 +14000,16 @@
         <v>15</v>
       </c>
       <c r="F344" s="5" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G344" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H344" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I344" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J344" s="7">
         <v>45615</v>
@@ -14032,16 +14035,16 @@
         <v>15</v>
       </c>
       <c r="F345" s="5" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G345" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H345" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I345" s="5" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="J345" s="7">
         <v>45741</v>
@@ -14067,16 +14070,16 @@
         <v>15</v>
       </c>
       <c r="F346" s="5" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G346" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H346" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I346" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="J346" s="7">
         <v>45967</v>
@@ -14102,16 +14105,16 @@
         <v>15</v>
       </c>
       <c r="F347" s="5" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="G347" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H347" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I347" s="5" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J347" s="7">
         <v>45686</v>
@@ -14137,16 +14140,16 @@
         <v>15</v>
       </c>
       <c r="F348" s="5" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="G348" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H348" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I348" s="5" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J348" s="7">
         <v>45678</v>
@@ -14172,16 +14175,16 @@
         <v>15</v>
       </c>
       <c r="F349" s="5" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="G349" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H349" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I349" s="5" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J349" s="7">
         <v>44384</v>
@@ -14207,16 +14210,16 @@
         <v>15</v>
       </c>
       <c r="F350" s="5" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="G350" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H350" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I350" s="5" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J350" s="7">
         <v>45125</v>
@@ -14242,14 +14245,14 @@
         <v>12</v>
       </c>
       <c r="F351" s="5" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="G351" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H351" s="5"/>
       <c r="I351" s="5" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="J351" s="7">
         <v>45667</v>
@@ -14275,14 +14278,14 @@
         <v>32</v>
       </c>
       <c r="F352" s="5" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="G352" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H352" s="5"/>
       <c r="I352" s="5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J352" s="7">
         <v>45667</v>
@@ -14308,14 +14311,14 @@
         <v>12</v>
       </c>
       <c r="F353" s="5" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="G353" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H353" s="5"/>
       <c r="I353" s="5" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="J353" s="7">
         <v>45532</v>
@@ -14341,14 +14344,14 @@
         <v>32</v>
       </c>
       <c r="F354" s="5" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="G354" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H354" s="5"/>
       <c r="I354" s="5" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="J354" s="7">
         <v>45532</v>
@@ -14374,14 +14377,14 @@
         <v>19</v>
       </c>
       <c r="F355" s="5" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="G355" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H355" s="5"/>
       <c r="I355" s="5" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J355" s="7">
         <v>45715</v>
@@ -14407,16 +14410,16 @@
         <v>15</v>
       </c>
       <c r="F356" s="5" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="G356" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H356" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I356" s="5" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="J356" s="7">
         <v>45615</v>
@@ -14442,16 +14445,16 @@
         <v>15</v>
       </c>
       <c r="F357" s="5" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="G357" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H357" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I357" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J357" s="7">
         <v>45686</v>
@@ -14477,16 +14480,16 @@
         <v>15</v>
       </c>
       <c r="F358" s="5" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G358" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H358" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I358" s="5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J358" s="7">
         <v>45639</v>
@@ -14512,16 +14515,16 @@
         <v>15</v>
       </c>
       <c r="F359" s="5" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="G359" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H359" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I359" s="5" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="J359" s="7">
         <v>44663</v>
@@ -14547,16 +14550,16 @@
         <v>15</v>
       </c>
       <c r="F360" s="5" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="G360" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H360" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I360" s="5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="J360" s="7">
         <v>45686</v>
@@ -14582,16 +14585,16 @@
         <v>15</v>
       </c>
       <c r="F361" s="5" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="G361" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H361" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I361" s="5" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="J361" s="7">
         <v>45531</v>
@@ -14617,14 +14620,14 @@
         <v>12</v>
       </c>
       <c r="F362" s="5" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="G362" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H362" s="5"/>
       <c r="I362" s="5" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J362" s="7">
         <v>44890</v>
@@ -14650,14 +14653,14 @@
         <v>32</v>
       </c>
       <c r="F363" s="5" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="G363" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H363" s="5"/>
       <c r="I363" s="5" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="J363" s="7">
         <v>44890</v>
@@ -14683,16 +14686,16 @@
         <v>15</v>
       </c>
       <c r="F364" s="5" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="G364" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H364" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I364" s="5" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="J364" s="7">
         <v>45828</v>
@@ -14718,14 +14721,14 @@
         <v>12</v>
       </c>
       <c r="F365" s="5" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="G365" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H365" s="5"/>
       <c r="I365" s="5" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="J365" s="7">
         <v>45986</v>
@@ -14751,14 +14754,14 @@
         <v>32</v>
       </c>
       <c r="F366" s="5" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="G366" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H366" s="5"/>
       <c r="I366" s="5" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="J366" s="7">
         <v>45986</v>
@@ -14784,16 +14787,16 @@
         <v>15</v>
       </c>
       <c r="F367" s="5" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G367" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H367" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I367" s="5" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J367" s="7">
         <v>45615</v>
@@ -14819,16 +14822,16 @@
         <v>15</v>
       </c>
       <c r="F368" s="5" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G368" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H368" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I368" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="J368" s="7">
         <v>45730</v>
@@ -14854,16 +14857,16 @@
         <v>15</v>
       </c>
       <c r="F369" s="5" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G369" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H369" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I369" s="5" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="J369" s="7">
         <v>45833</v>
@@ -14889,16 +14892,16 @@
         <v>15</v>
       </c>
       <c r="F370" s="5" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G370" s="5" t="s">
         <v>46</v>
       </c>
       <c r="H370" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I370" s="5" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="J370" s="7">
         <v>44573</v>
@@ -14924,16 +14927,16 @@
         <v>15</v>
       </c>
       <c r="F371" s="5" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G371" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H371" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I371" s="5" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="J371" s="7">
         <v>45967</v>
@@ -14959,16 +14962,16 @@
         <v>15</v>
       </c>
       <c r="F372" s="5" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="G372" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H372" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I372" s="5" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="J372" s="7">
         <v>45800</v>
@@ -14994,16 +14997,16 @@
         <v>15</v>
       </c>
       <c r="F373" s="5" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G373" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H373" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I373" s="5" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="J373" s="7">
         <v>45868</v>
@@ -15029,16 +15032,16 @@
         <v>15</v>
       </c>
       <c r="F374" s="5" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G374" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H374" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I374" s="5" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="J374" s="7">
         <v>45686</v>
@@ -15064,14 +15067,14 @@
         <v>12</v>
       </c>
       <c r="F375" s="5" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="G375" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H375" s="5"/>
       <c r="I375" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="J375" s="7">
         <v>44920</v>
@@ -15097,14 +15100,14 @@
         <v>32</v>
       </c>
       <c r="F376" s="5" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="G376" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H376" s="5"/>
       <c r="I376" s="5" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="J376" s="7">
         <v>44890</v>
@@ -15130,14 +15133,14 @@
         <v>66</v>
       </c>
       <c r="F377" s="5" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="G377" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H377" s="5"/>
       <c r="I377" s="5" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="J377" s="7">
         <v>44890</v>
@@ -15163,14 +15166,14 @@
         <v>12</v>
       </c>
       <c r="F378" s="5" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="G378" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H378" s="5"/>
       <c r="I378" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="J378" s="7">
         <v>45986</v>
@@ -15196,14 +15199,14 @@
         <v>32</v>
       </c>
       <c r="F379" s="5" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="G379" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H379" s="5"/>
       <c r="I379" s="5" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="J379" s="7">
         <v>44890</v>
@@ -15229,14 +15232,14 @@
         <v>66</v>
       </c>
       <c r="F380" s="5" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="G380" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H380" s="5"/>
       <c r="I380" s="5" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="J380" s="7">
         <v>44890</v>
@@ -15262,14 +15265,14 @@
         <v>12</v>
       </c>
       <c r="F381" s="5" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="G381" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H381" s="5"/>
       <c r="I381" s="5" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="J381" s="7">
         <v>45174</v>
@@ -15295,14 +15298,14 @@
         <v>32</v>
       </c>
       <c r="F382" s="5" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="G382" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H382" s="5"/>
       <c r="I382" s="5" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="J382" s="7">
         <v>45175</v>
@@ -15328,14 +15331,14 @@
         <v>66</v>
       </c>
       <c r="F383" s="5" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="G383" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H383" s="5"/>
       <c r="I383" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="J383" s="7">
         <v>45175</v>
@@ -15361,14 +15364,14 @@
         <v>12</v>
       </c>
       <c r="F384" s="5" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="G384" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H384" s="5"/>
       <c r="I384" s="5" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="J384" s="7">
         <v>44939</v>
@@ -15394,14 +15397,14 @@
         <v>32</v>
       </c>
       <c r="F385" s="5" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="G385" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H385" s="5"/>
       <c r="I385" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="J385" s="7">
         <v>44939</v>
@@ -15427,14 +15430,14 @@
         <v>66</v>
       </c>
       <c r="F386" s="5" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="G386" s="5" t="s">
         <v>28</v>
       </c>
       <c r="H386" s="5"/>
       <c r="I386" s="5" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="J386" s="7">
         <v>44939</v>
@@ -15460,14 +15463,14 @@
         <v>19</v>
       </c>
       <c r="F387" s="5" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="G387" s="5" t="s">
         <v>149</v>
       </c>
       <c r="H387" s="5"/>
       <c r="I387" s="5" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="J387" s="7">
         <v>44939</v>
@@ -15493,14 +15496,14 @@
         <v>15</v>
       </c>
       <c r="F388" s="5" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G388" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H388" s="5"/>
       <c r="I388" s="5" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="J388" s="7">
         <v>45341</v>
@@ -15526,14 +15529,14 @@
         <v>12</v>
       </c>
       <c r="F389" s="5" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="G389" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H389" s="5"/>
       <c r="I389" s="5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="J389" s="7">
         <v>45622</v>
@@ -15559,14 +15562,14 @@
         <v>32</v>
       </c>
       <c r="F390" s="5" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="G390" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H390" s="5"/>
       <c r="I390" s="5" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="J390" s="7">
         <v>45622</v>
@@ -15592,14 +15595,14 @@
         <v>66</v>
       </c>
       <c r="F391" s="5" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="G391" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H391" s="5"/>
       <c r="I391" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="J391" s="7">
         <v>45622</v>
@@ -15625,14 +15628,14 @@
         <v>19</v>
       </c>
       <c r="F392" s="5" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="G392" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H392" s="5"/>
       <c r="I392" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J392" s="7">
         <v>45622</v>
@@ -15658,14 +15661,14 @@
         <v>83</v>
       </c>
       <c r="F393" s="5" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="G393" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H393" s="5"/>
       <c r="I393" s="5" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="J393" s="7">
         <v>45622</v>
@@ -15691,14 +15694,14 @@
         <v>70</v>
       </c>
       <c r="F394" s="5" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="G394" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H394" s="5"/>
       <c r="I394" s="5" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="J394" s="7">
         <v>45622</v>
@@ -15724,14 +15727,14 @@
         <v>12</v>
       </c>
       <c r="F395" s="5" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G395" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H395" s="5"/>
       <c r="I395" s="5" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="J395" s="7">
         <v>45447</v>
@@ -15757,14 +15760,14 @@
         <v>32</v>
       </c>
       <c r="F396" s="5" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G396" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H396" s="5"/>
       <c r="I396" s="5" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="J396" s="7">
         <v>45447</v>
@@ -15790,14 +15793,14 @@
         <v>66</v>
       </c>
       <c r="F397" s="5" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G397" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H397" s="5"/>
       <c r="I397" s="5" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="J397" s="7">
         <v>45447</v>
@@ -15823,14 +15826,14 @@
         <v>19</v>
       </c>
       <c r="F398" s="5" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G398" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H398" s="5"/>
       <c r="I398" s="5" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="J398" s="7">
         <v>45447</v>
@@ -15856,14 +15859,14 @@
         <v>83</v>
       </c>
       <c r="F399" s="5" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G399" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H399" s="5"/>
       <c r="I399" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="J399" s="7">
         <v>45447</v>
@@ -15889,14 +15892,14 @@
         <v>70</v>
       </c>
       <c r="F400" s="5" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G400" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H400" s="5"/>
       <c r="I400" s="5" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="J400" s="7">
         <v>45447</v>
@@ -15922,14 +15925,14 @@
         <v>72</v>
       </c>
       <c r="F401" s="5" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G401" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H401" s="5"/>
       <c r="I401" s="5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="J401" s="7">
         <v>45447</v>
@@ -15955,14 +15958,14 @@
         <v>74</v>
       </c>
       <c r="F402" s="5" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G402" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H402" s="5"/>
       <c r="I402" s="5" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="J402" s="7">
         <v>45447</v>
@@ -15988,14 +15991,14 @@
         <v>76</v>
       </c>
       <c r="F403" s="5" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G403" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H403" s="5"/>
       <c r="I403" s="5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="J403" s="7">
         <v>45447</v>
@@ -16021,14 +16024,14 @@
         <v>78</v>
       </c>
       <c r="F404" s="5" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G404" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H404" s="5"/>
       <c r="I404" s="5" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="J404" s="7">
         <v>45447</v>
@@ -16051,17 +16054,17 @@
         <v>18167</v>
       </c>
       <c r="E405" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F405" s="5" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G405" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H405" s="5"/>
       <c r="I405" s="5" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="J405" s="7">
         <v>45447</v>
@@ -16084,17 +16087,17 @@
         <v>18167</v>
       </c>
       <c r="E406" s="5" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F406" s="5" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G406" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H406" s="5"/>
       <c r="I406" s="5" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="J406" s="7">
         <v>45447</v>
@@ -16117,17 +16120,17 @@
         <v>18167</v>
       </c>
       <c r="E407" s="5" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F407" s="5" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G407" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H407" s="5"/>
       <c r="I407" s="5" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="J407" s="7">
         <v>45447</v>
@@ -16153,16 +16156,16 @@
         <v>15</v>
       </c>
       <c r="F408" s="5" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G408" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H408" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I408" s="5" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="J408" s="7">
         <v>45630</v>
@@ -16188,16 +16191,16 @@
         <v>15</v>
       </c>
       <c r="F409" s="5" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G409" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H409" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I409" s="5" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="J409" s="7">
         <v>45630</v>
@@ -16223,14 +16226,14 @@
         <v>32</v>
       </c>
       <c r="F410" s="5" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="G410" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H410" s="5"/>
       <c r="I410" s="5" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J410" s="7">
         <v>45461</v>
@@ -16256,14 +16259,14 @@
         <v>66</v>
       </c>
       <c r="F411" s="5" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="G411" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H411" s="5"/>
       <c r="I411" s="5" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="J411" s="7">
         <v>45461</v>
@@ -16289,14 +16292,14 @@
         <v>12</v>
       </c>
       <c r="F412" s="5" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="G412" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H412" s="5"/>
       <c r="I412" s="5" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="J412" s="7">
         <v>45463</v>
@@ -16322,14 +16325,14 @@
         <v>32</v>
       </c>
       <c r="F413" s="5" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="G413" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H413" s="5"/>
       <c r="I413" s="5" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="J413" s="7">
         <v>45463</v>
@@ -16355,14 +16358,14 @@
         <v>19</v>
       </c>
       <c r="F414" s="5" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="G414" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H414" s="5"/>
       <c r="I414" s="5" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="J414" s="7">
         <v>46558</v>
@@ -16388,14 +16391,14 @@
         <v>83</v>
       </c>
       <c r="F415" s="5" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="G415" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H415" s="5"/>
       <c r="I415" s="5" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="J415" s="7">
         <v>45463</v>
@@ -16421,14 +16424,14 @@
         <v>12</v>
       </c>
       <c r="F416" s="5" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="G416" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H416" s="5"/>
       <c r="I416" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="J416" s="7">
         <v>45944</v>
@@ -16454,14 +16457,14 @@
         <v>32</v>
       </c>
       <c r="F417" s="5" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="G417" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H417" s="5"/>
       <c r="I417" s="5" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="J417" s="7">
         <v>45944</v>
@@ -16487,14 +16490,14 @@
         <v>66</v>
       </c>
       <c r="F418" s="5" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="G418" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H418" s="5"/>
       <c r="I418" s="5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J418" s="7">
         <v>45944</v>
@@ -16520,14 +16523,14 @@
         <v>72</v>
       </c>
       <c r="F419" s="5" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="G419" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H419" s="5"/>
       <c r="I419" s="5" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J419" s="7">
         <v>45944</v>
@@ -16553,14 +16556,14 @@
         <v>74</v>
       </c>
       <c r="F420" s="5" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="G420" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H420" s="5"/>
       <c r="I420" s="5" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="J420" s="7">
         <v>45944</v>
@@ -16586,14 +16589,14 @@
         <v>76</v>
       </c>
       <c r="F421" s="5" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="G421" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H421" s="5"/>
       <c r="I421" s="5" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="J421" s="7">
         <v>45944</v>
@@ -16619,14 +16622,14 @@
         <v>78</v>
       </c>
       <c r="F422" s="5" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="G422" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H422" s="5"/>
       <c r="I422" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="J422" s="7">
         <v>45944</v>
@@ -16649,17 +16652,17 @@
         <v>18181</v>
       </c>
       <c r="E423" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F423" s="5" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="G423" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H423" s="5"/>
       <c r="I423" s="5" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J423" s="7">
         <v>45944</v>
@@ -16685,14 +16688,14 @@
         <v>12</v>
       </c>
       <c r="F424" s="5" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="G424" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H424" s="5"/>
       <c r="I424" s="5" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="J424" s="7">
         <v>45545</v>
@@ -16718,14 +16721,14 @@
         <v>32</v>
       </c>
       <c r="F425" s="5" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="G425" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H425" s="5"/>
       <c r="I425" s="5" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="J425" s="7">
         <v>45545</v>
@@ -16751,14 +16754,14 @@
         <v>12</v>
       </c>
       <c r="F426" s="5" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="G426" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H426" s="5"/>
       <c r="I426" s="5" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="J426" s="7">
         <v>45539</v>
@@ -16784,14 +16787,14 @@
         <v>32</v>
       </c>
       <c r="F427" s="5" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="G427" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H427" s="5"/>
       <c r="I427" s="5" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="J427" s="7">
         <v>45539</v>
@@ -16817,14 +16820,14 @@
         <v>12</v>
       </c>
       <c r="F428" s="5" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="G428" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H428" s="5"/>
       <c r="I428" s="5" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="J428" s="7">
         <v>45503</v>
@@ -16850,14 +16853,14 @@
         <v>32</v>
       </c>
       <c r="F429" s="5" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="G429" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H429" s="5"/>
       <c r="I429" s="5" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="J429" s="7">
         <v>45503</v>
@@ -16883,14 +16886,14 @@
         <v>12</v>
       </c>
       <c r="F430" s="5" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="G430" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H430" s="5"/>
       <c r="I430" s="5" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="J430" s="7">
         <v>45503</v>
@@ -16916,14 +16919,14 @@
         <v>32</v>
       </c>
       <c r="F431" s="5" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="G431" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H431" s="5"/>
       <c r="I431" s="5" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="J431" s="7">
         <v>45503</v>
@@ -16949,16 +16952,16 @@
         <v>15</v>
       </c>
       <c r="F432" s="5" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="G432" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H432" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I432" s="5" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="J432" s="7">
         <v>45785</v>
@@ -16984,16 +16987,16 @@
         <v>15</v>
       </c>
       <c r="F433" s="5" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G433" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H433" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I433" s="5" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="J433" s="7">
         <v>45610</v>
@@ -17019,16 +17022,16 @@
         <v>15</v>
       </c>
       <c r="F434" s="5" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="G434" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H434" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I434" s="5" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="J434" s="7">
         <v>45848</v>
@@ -17054,16 +17057,16 @@
         <v>15</v>
       </c>
       <c r="F435" s="5" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="G435" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H435" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I435" s="5" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="J435" s="7">
         <v>45610</v>
@@ -17089,14 +17092,14 @@
         <v>15</v>
       </c>
       <c r="F436" s="5" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G436" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H436" s="5"/>
       <c r="I436" s="5" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="J436" s="7">
         <v>45624</v>
@@ -17122,14 +17125,14 @@
         <v>70</v>
       </c>
       <c r="F437" s="5" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G437" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H437" s="5"/>
       <c r="I437" s="5" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="J437" s="7">
         <v>45624</v>
@@ -17155,16 +17158,16 @@
         <v>15</v>
       </c>
       <c r="F438" s="5" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="G438" s="5" t="s">
         <v>13</v>
       </c>
       <c r="H438" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I438" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="J438" s="7">
         <v>45914</v>
@@ -17174,2254 +17177,2259 @@
       </c>
     </row>
     <row r="439" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J439" s="9"/>
-      <c r="K439" s="9"/>
+      <c r="J439" s="8"/>
+      <c r="K439" s="8"/>
     </row>
     <row r="440" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J440" s="9"/>
-      <c r="K440" s="9"/>
+      <c r="J440" s="8"/>
+      <c r="K440" s="8"/>
     </row>
     <row r="441" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J441" s="9"/>
-      <c r="K441" s="9"/>
+      <c r="J441" s="8"/>
+      <c r="K441" s="8"/>
     </row>
     <row r="442" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J442" s="9"/>
-      <c r="K442" s="9"/>
+      <c r="J442" s="8"/>
+      <c r="K442" s="8"/>
     </row>
     <row r="443" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J443" s="9"/>
-      <c r="K443" s="9"/>
+      <c r="J443" s="8"/>
+      <c r="K443" s="8"/>
     </row>
     <row r="444" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J444" s="9"/>
-      <c r="K444" s="9"/>
+      <c r="J444" s="8"/>
+      <c r="K444" s="8"/>
     </row>
     <row r="445" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J445" s="9"/>
-      <c r="K445" s="9"/>
+      <c r="J445" s="8"/>
+      <c r="K445" s="8"/>
     </row>
     <row r="446" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J446" s="9"/>
-      <c r="K446" s="9"/>
+      <c r="J446" s="8"/>
+      <c r="K446" s="8"/>
     </row>
     <row r="447" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J447" s="9"/>
-      <c r="K447" s="9"/>
+      <c r="J447" s="8"/>
+      <c r="K447" s="8"/>
     </row>
     <row r="448" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J448" s="9"/>
-      <c r="K448" s="9"/>
+      <c r="J448" s="8"/>
+      <c r="K448" s="8"/>
     </row>
     <row r="449" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J449" s="9"/>
-      <c r="K449" s="9"/>
+      <c r="J449" s="8"/>
+      <c r="K449" s="8"/>
     </row>
     <row r="450" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J450" s="9"/>
-      <c r="K450" s="9"/>
+      <c r="J450" s="8"/>
+      <c r="K450" s="8"/>
     </row>
     <row r="451" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J451" s="9"/>
-      <c r="K451" s="9"/>
+      <c r="J451" s="8"/>
+      <c r="K451" s="8"/>
     </row>
     <row r="452" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J452" s="9"/>
-      <c r="K452" s="9"/>
+      <c r="J452" s="8"/>
+      <c r="K452" s="8"/>
     </row>
     <row r="453" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J453" s="9"/>
-      <c r="K453" s="9"/>
+      <c r="J453" s="8"/>
+      <c r="K453" s="8"/>
     </row>
     <row r="454" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J454" s="9"/>
-      <c r="K454" s="9"/>
+      <c r="J454" s="8"/>
+      <c r="K454" s="8"/>
     </row>
     <row r="455" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J455" s="9"/>
-      <c r="K455" s="9"/>
+      <c r="J455" s="8"/>
+      <c r="K455" s="8"/>
     </row>
     <row r="456" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J456" s="9"/>
-      <c r="K456" s="9"/>
+      <c r="J456" s="8"/>
+      <c r="K456" s="8"/>
     </row>
     <row r="457" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J457" s="9"/>
-      <c r="K457" s="9"/>
+      <c r="J457" s="8"/>
+      <c r="K457" s="8"/>
     </row>
     <row r="458" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J458" s="9"/>
-      <c r="K458" s="9"/>
+      <c r="J458" s="8"/>
+      <c r="K458" s="8"/>
     </row>
     <row r="459" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J459" s="9"/>
-      <c r="K459" s="9"/>
+      <c r="J459" s="8"/>
+      <c r="K459" s="8"/>
     </row>
     <row r="460" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J460" s="9"/>
-      <c r="K460" s="9"/>
+      <c r="J460" s="8"/>
+      <c r="K460" s="8"/>
     </row>
     <row r="461" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J461" s="9"/>
-      <c r="K461" s="9"/>
+      <c r="J461" s="8"/>
+      <c r="K461" s="8"/>
     </row>
     <row r="462" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J462" s="9"/>
-      <c r="K462" s="9"/>
+      <c r="J462" s="8"/>
+      <c r="K462" s="8"/>
     </row>
     <row r="463" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J463" s="9"/>
-      <c r="K463" s="9"/>
+      <c r="J463" s="8"/>
+      <c r="K463" s="8"/>
     </row>
     <row r="464" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J464" s="9"/>
-      <c r="K464" s="9"/>
+      <c r="J464" s="8"/>
+      <c r="K464" s="8"/>
     </row>
     <row r="465" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J465" s="9"/>
-      <c r="K465" s="9"/>
+      <c r="J465" s="8"/>
+      <c r="K465" s="8"/>
     </row>
     <row r="466" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J466" s="9"/>
-      <c r="K466" s="9"/>
+      <c r="J466" s="8"/>
+      <c r="K466" s="8"/>
     </row>
     <row r="467" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J467" s="9"/>
-      <c r="K467" s="9"/>
+      <c r="J467" s="8"/>
+      <c r="K467" s="8"/>
     </row>
     <row r="468" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J468" s="9"/>
-      <c r="K468" s="9"/>
+      <c r="J468" s="8"/>
+      <c r="K468" s="8"/>
     </row>
     <row r="469" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J469" s="9"/>
-      <c r="K469" s="9"/>
+      <c r="J469" s="8"/>
+      <c r="K469" s="8"/>
     </row>
     <row r="470" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J470" s="9"/>
-      <c r="K470" s="9"/>
+      <c r="J470" s="8"/>
+      <c r="K470" s="8"/>
     </row>
     <row r="471" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J471" s="9"/>
-      <c r="K471" s="9"/>
+      <c r="J471" s="8"/>
+      <c r="K471" s="8"/>
     </row>
     <row r="472" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J472" s="9"/>
-      <c r="K472" s="9"/>
+      <c r="J472" s="8"/>
+      <c r="K472" s="8"/>
     </row>
     <row r="473" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J473" s="9"/>
-      <c r="K473" s="9"/>
+      <c r="J473" s="8"/>
+      <c r="K473" s="8"/>
     </row>
     <row r="474" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J474" s="9"/>
-      <c r="K474" s="9"/>
+      <c r="J474" s="8"/>
+      <c r="K474" s="8"/>
     </row>
     <row r="475" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J475" s="9"/>
-      <c r="K475" s="9"/>
+      <c r="J475" s="8"/>
+      <c r="K475" s="8"/>
     </row>
     <row r="476" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J476" s="9"/>
-      <c r="K476" s="9"/>
+      <c r="J476" s="8"/>
+      <c r="K476" s="8"/>
     </row>
     <row r="477" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J477" s="9"/>
-      <c r="K477" s="9"/>
+      <c r="J477" s="8"/>
+      <c r="K477" s="8"/>
     </row>
     <row r="478" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J478" s="9"/>
-      <c r="K478" s="9"/>
+      <c r="J478" s="8"/>
+      <c r="K478" s="8"/>
     </row>
     <row r="479" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J479" s="9"/>
-      <c r="K479" s="9"/>
+      <c r="J479" s="8"/>
+      <c r="K479" s="8"/>
     </row>
     <row r="480" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J480" s="9"/>
-      <c r="K480" s="9"/>
+      <c r="J480" s="8"/>
+      <c r="K480" s="8"/>
     </row>
     <row r="481" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J481" s="9"/>
-      <c r="K481" s="9"/>
+      <c r="J481" s="8"/>
+      <c r="K481" s="8"/>
     </row>
     <row r="482" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J482" s="9"/>
-      <c r="K482" s="9"/>
+      <c r="J482" s="8"/>
+      <c r="K482" s="8"/>
     </row>
     <row r="483" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J483" s="9"/>
-      <c r="K483" s="9"/>
+      <c r="J483" s="8"/>
+      <c r="K483" s="8"/>
     </row>
     <row r="484" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J484" s="9"/>
-      <c r="K484" s="9"/>
+      <c r="J484" s="8"/>
+      <c r="K484" s="8"/>
     </row>
     <row r="485" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J485" s="9"/>
-      <c r="K485" s="9"/>
+      <c r="J485" s="8"/>
+      <c r="K485" s="8"/>
     </row>
     <row r="486" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J486" s="9"/>
-      <c r="K486" s="9"/>
+      <c r="J486" s="8"/>
+      <c r="K486" s="8"/>
     </row>
     <row r="487" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J487" s="9"/>
-      <c r="K487" s="9"/>
+      <c r="J487" s="8"/>
+      <c r="K487" s="8"/>
     </row>
     <row r="488" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J488" s="9"/>
-      <c r="K488" s="9"/>
+      <c r="J488" s="8"/>
+      <c r="K488" s="8"/>
     </row>
     <row r="489" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J489" s="9"/>
-      <c r="K489" s="9"/>
+      <c r="J489" s="8"/>
+      <c r="K489" s="8"/>
     </row>
     <row r="490" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J490" s="9"/>
-      <c r="K490" s="9"/>
+      <c r="J490" s="8"/>
+      <c r="K490" s="8"/>
     </row>
     <row r="491" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J491" s="9"/>
-      <c r="K491" s="9"/>
+      <c r="J491" s="8"/>
+      <c r="K491" s="8"/>
     </row>
     <row r="492" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J492" s="9"/>
-      <c r="K492" s="9"/>
+      <c r="J492" s="8"/>
+      <c r="K492" s="8"/>
     </row>
     <row r="493" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J493" s="9"/>
-      <c r="K493" s="9"/>
+      <c r="J493" s="8"/>
+      <c r="K493" s="8"/>
     </row>
     <row r="494" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J494" s="9"/>
-      <c r="K494" s="9"/>
+      <c r="J494" s="8"/>
+      <c r="K494" s="8"/>
     </row>
     <row r="495" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J495" s="9"/>
-      <c r="K495" s="9"/>
+      <c r="J495" s="8"/>
+      <c r="K495" s="8"/>
     </row>
     <row r="496" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J496" s="9"/>
-      <c r="K496" s="9"/>
+      <c r="J496" s="8"/>
+      <c r="K496" s="8"/>
     </row>
     <row r="497" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J497" s="9"/>
-      <c r="K497" s="9"/>
+      <c r="J497" s="8"/>
+      <c r="K497" s="8"/>
     </row>
     <row r="498" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J498" s="9"/>
-      <c r="K498" s="9"/>
+      <c r="J498" s="8"/>
+      <c r="K498" s="8"/>
     </row>
     <row r="499" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J499" s="9"/>
-      <c r="K499" s="9"/>
+      <c r="J499" s="8"/>
+      <c r="K499" s="8"/>
     </row>
     <row r="500" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J500" s="9"/>
-      <c r="K500" s="9"/>
+      <c r="J500" s="8"/>
+      <c r="K500" s="8"/>
     </row>
     <row r="501" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J501" s="9"/>
-      <c r="K501" s="9"/>
+      <c r="J501" s="8"/>
+      <c r="K501" s="8"/>
     </row>
     <row r="502" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J502" s="9"/>
-      <c r="K502" s="9"/>
+      <c r="J502" s="8"/>
+      <c r="K502" s="8"/>
     </row>
     <row r="503" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J503" s="9"/>
-      <c r="K503" s="9"/>
+      <c r="J503" s="8"/>
+      <c r="K503" s="8"/>
     </row>
     <row r="504" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J504" s="9"/>
-      <c r="K504" s="9"/>
+      <c r="J504" s="8"/>
+      <c r="K504" s="8"/>
     </row>
     <row r="505" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J505" s="9"/>
-      <c r="K505" s="9"/>
+      <c r="J505" s="8"/>
+      <c r="K505" s="8"/>
     </row>
     <row r="506" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J506" s="9"/>
-      <c r="K506" s="9"/>
+      <c r="J506" s="8"/>
+      <c r="K506" s="8"/>
     </row>
     <row r="507" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J507" s="9"/>
-      <c r="K507" s="9"/>
+      <c r="J507" s="8"/>
+      <c r="K507" s="8"/>
     </row>
     <row r="508" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J508" s="9"/>
-      <c r="K508" s="9"/>
+      <c r="J508" s="8"/>
+      <c r="K508" s="8"/>
     </row>
     <row r="509" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J509" s="9"/>
-      <c r="K509" s="9"/>
+      <c r="J509" s="8"/>
+      <c r="K509" s="8"/>
     </row>
     <row r="510" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J510" s="9"/>
-      <c r="K510" s="9"/>
+      <c r="J510" s="8"/>
+      <c r="K510" s="8"/>
     </row>
     <row r="511" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J511" s="9"/>
-      <c r="K511" s="9"/>
+      <c r="J511" s="8"/>
+      <c r="K511" s="8"/>
     </row>
     <row r="512" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J512" s="9"/>
-      <c r="K512" s="9"/>
+      <c r="J512" s="8"/>
+      <c r="K512" s="8"/>
     </row>
     <row r="513" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J513" s="9"/>
-      <c r="K513" s="9"/>
+      <c r="J513" s="8"/>
+      <c r="K513" s="8"/>
     </row>
     <row r="514" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J514" s="9"/>
-      <c r="K514" s="9"/>
+      <c r="J514" s="8"/>
+      <c r="K514" s="8"/>
     </row>
     <row r="515" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J515" s="9"/>
-      <c r="K515" s="9"/>
+      <c r="J515" s="8"/>
+      <c r="K515" s="8"/>
     </row>
     <row r="516" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J516" s="9"/>
-      <c r="K516" s="9"/>
+      <c r="J516" s="8"/>
+      <c r="K516" s="8"/>
     </row>
     <row r="517" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J517" s="9"/>
-      <c r="K517" s="9"/>
+      <c r="J517" s="8"/>
+      <c r="K517" s="8"/>
     </row>
     <row r="518" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J518" s="9"/>
-      <c r="K518" s="9"/>
+      <c r="J518" s="8"/>
+      <c r="K518" s="8"/>
     </row>
     <row r="519" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J519" s="9"/>
-      <c r="K519" s="9"/>
+      <c r="J519" s="8"/>
+      <c r="K519" s="8"/>
     </row>
     <row r="520" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J520" s="9"/>
-      <c r="K520" s="9"/>
+      <c r="J520" s="8"/>
+      <c r="K520" s="8"/>
     </row>
     <row r="521" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J521" s="9"/>
-      <c r="K521" s="9"/>
+      <c r="J521" s="8"/>
+      <c r="K521" s="8"/>
     </row>
     <row r="522" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J522" s="9"/>
-      <c r="K522" s="9"/>
+      <c r="J522" s="8"/>
+      <c r="K522" s="8"/>
     </row>
     <row r="523" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J523" s="9"/>
-      <c r="K523" s="9"/>
+      <c r="J523" s="8"/>
+      <c r="K523" s="8"/>
     </row>
     <row r="524" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J524" s="9"/>
-      <c r="K524" s="9"/>
+      <c r="J524" s="8"/>
+      <c r="K524" s="8"/>
     </row>
     <row r="525" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J525" s="9"/>
-      <c r="K525" s="9"/>
+      <c r="J525" s="8"/>
+      <c r="K525" s="8"/>
     </row>
     <row r="526" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J526" s="9"/>
-      <c r="K526" s="9"/>
+      <c r="J526" s="8"/>
+      <c r="K526" s="8"/>
     </row>
     <row r="527" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J527" s="9"/>
-      <c r="K527" s="9"/>
+      <c r="J527" s="8"/>
+      <c r="K527" s="8"/>
     </row>
     <row r="528" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J528" s="9"/>
-      <c r="K528" s="9"/>
+      <c r="J528" s="8"/>
+      <c r="K528" s="8"/>
     </row>
     <row r="529" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J529" s="9"/>
-      <c r="K529" s="9"/>
+      <c r="J529" s="8"/>
+      <c r="K529" s="8"/>
     </row>
     <row r="530" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J530" s="9"/>
-      <c r="K530" s="9"/>
+      <c r="J530" s="8"/>
+      <c r="K530" s="8"/>
     </row>
     <row r="531" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J531" s="9"/>
-      <c r="K531" s="9"/>
+      <c r="J531" s="8"/>
+      <c r="K531" s="8"/>
     </row>
     <row r="532" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J532" s="9"/>
-      <c r="K532" s="9"/>
+      <c r="J532" s="8"/>
+      <c r="K532" s="8"/>
     </row>
     <row r="533" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J533" s="9"/>
-      <c r="K533" s="9"/>
+      <c r="J533" s="8"/>
+      <c r="K533" s="8"/>
     </row>
     <row r="534" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J534" s="9"/>
-      <c r="K534" s="9"/>
+      <c r="J534" s="8"/>
+      <c r="K534" s="8"/>
     </row>
     <row r="535" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J535" s="9"/>
-      <c r="K535" s="9"/>
+      <c r="J535" s="8"/>
+      <c r="K535" s="8"/>
     </row>
     <row r="536" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J536" s="9"/>
-      <c r="K536" s="9"/>
+      <c r="J536" s="8"/>
+      <c r="K536" s="8"/>
     </row>
     <row r="537" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J537" s="9"/>
-      <c r="K537" s="9"/>
+      <c r="J537" s="8"/>
+      <c r="K537" s="8"/>
     </row>
     <row r="538" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J538" s="9"/>
-      <c r="K538" s="9"/>
+      <c r="J538" s="8"/>
+      <c r="K538" s="8"/>
     </row>
     <row r="539" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J539" s="9"/>
-      <c r="K539" s="9"/>
+      <c r="J539" s="8"/>
+      <c r="K539" s="8"/>
     </row>
     <row r="540" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J540" s="9"/>
-      <c r="K540" s="9"/>
+      <c r="J540" s="8"/>
+      <c r="K540" s="8"/>
     </row>
     <row r="541" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J541" s="9"/>
-      <c r="K541" s="9"/>
+      <c r="J541" s="8"/>
+      <c r="K541" s="8"/>
     </row>
     <row r="542" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J542" s="9"/>
-      <c r="K542" s="9"/>
+      <c r="J542" s="8"/>
+      <c r="K542" s="8"/>
     </row>
     <row r="543" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J543" s="9"/>
-      <c r="K543" s="9"/>
+      <c r="J543" s="8"/>
+      <c r="K543" s="8"/>
     </row>
     <row r="544" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J544" s="9"/>
-      <c r="K544" s="9"/>
+      <c r="J544" s="8"/>
+      <c r="K544" s="8"/>
     </row>
     <row r="545" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J545" s="9"/>
-      <c r="K545" s="9"/>
+      <c r="J545" s="8"/>
+      <c r="K545" s="8"/>
     </row>
     <row r="546" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J546" s="9"/>
-      <c r="K546" s="9"/>
+      <c r="J546" s="8"/>
+      <c r="K546" s="8"/>
     </row>
     <row r="547" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J547" s="9"/>
-      <c r="K547" s="9"/>
+      <c r="J547" s="8"/>
+      <c r="K547" s="8"/>
     </row>
     <row r="548" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J548" s="9"/>
-      <c r="K548" s="9"/>
+      <c r="J548" s="8"/>
+      <c r="K548" s="8"/>
     </row>
     <row r="549" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J549" s="9"/>
-      <c r="K549" s="9"/>
+      <c r="J549" s="8"/>
+      <c r="K549" s="8"/>
     </row>
     <row r="550" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J550" s="9"/>
-      <c r="K550" s="9"/>
+      <c r="J550" s="8"/>
+      <c r="K550" s="8"/>
     </row>
     <row r="551" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J551" s="9"/>
-      <c r="K551" s="9"/>
+      <c r="J551" s="8"/>
+      <c r="K551" s="8"/>
     </row>
     <row r="552" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J552" s="9"/>
-      <c r="K552" s="9"/>
+      <c r="J552" s="8"/>
+      <c r="K552" s="8"/>
     </row>
     <row r="553" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J553" s="9"/>
-      <c r="K553" s="9"/>
+      <c r="J553" s="8"/>
+      <c r="K553" s="8"/>
     </row>
     <row r="554" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J554" s="9"/>
-      <c r="K554" s="9"/>
+      <c r="J554" s="8"/>
+      <c r="K554" s="8"/>
     </row>
     <row r="555" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J555" s="9"/>
-      <c r="K555" s="9"/>
+      <c r="J555" s="8"/>
+      <c r="K555" s="8"/>
     </row>
     <row r="556" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J556" s="9"/>
-      <c r="K556" s="9"/>
+      <c r="J556" s="8"/>
+      <c r="K556" s="8"/>
     </row>
     <row r="557" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J557" s="9"/>
-      <c r="K557" s="9"/>
+      <c r="J557" s="8"/>
+      <c r="K557" s="8"/>
     </row>
     <row r="558" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J558" s="9"/>
-      <c r="K558" s="9"/>
+      <c r="J558" s="8"/>
+      <c r="K558" s="8"/>
     </row>
     <row r="559" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J559" s="9"/>
-      <c r="K559" s="9"/>
+      <c r="J559" s="8"/>
+      <c r="K559" s="8"/>
     </row>
     <row r="560" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J560" s="9"/>
-      <c r="K560" s="9"/>
+      <c r="J560" s="8"/>
+      <c r="K560" s="8"/>
     </row>
     <row r="561" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J561" s="9"/>
-      <c r="K561" s="9"/>
+      <c r="J561" s="8"/>
+      <c r="K561" s="8"/>
     </row>
     <row r="562" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J562" s="9"/>
-      <c r="K562" s="9"/>
+      <c r="J562" s="8"/>
+      <c r="K562" s="8"/>
     </row>
     <row r="563" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J563" s="9"/>
-      <c r="K563" s="9"/>
+      <c r="J563" s="8"/>
+      <c r="K563" s="8"/>
     </row>
     <row r="564" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J564" s="9"/>
-      <c r="K564" s="9"/>
+      <c r="J564" s="8"/>
+      <c r="K564" s="8"/>
     </row>
     <row r="565" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J565" s="9"/>
-      <c r="K565" s="9"/>
+      <c r="J565" s="8"/>
+      <c r="K565" s="8"/>
     </row>
     <row r="566" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J566" s="9"/>
-      <c r="K566" s="9"/>
+      <c r="J566" s="8"/>
+      <c r="K566" s="8"/>
     </row>
     <row r="567" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J567" s="9"/>
-      <c r="K567" s="9"/>
+      <c r="J567" s="8"/>
+      <c r="K567" s="8"/>
     </row>
     <row r="568" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J568" s="9"/>
-      <c r="K568" s="9"/>
+      <c r="J568" s="8"/>
+      <c r="K568" s="8"/>
     </row>
     <row r="569" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J569" s="9"/>
-      <c r="K569" s="9"/>
+      <c r="J569" s="8"/>
+      <c r="K569" s="8"/>
     </row>
     <row r="570" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J570" s="9"/>
-      <c r="K570" s="9"/>
+      <c r="J570" s="8"/>
+      <c r="K570" s="8"/>
     </row>
     <row r="571" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J571" s="9"/>
-      <c r="K571" s="9"/>
+      <c r="J571" s="8"/>
+      <c r="K571" s="8"/>
     </row>
     <row r="572" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J572" s="9"/>
-      <c r="K572" s="9"/>
+      <c r="J572" s="8"/>
+      <c r="K572" s="8"/>
     </row>
     <row r="573" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J573" s="9"/>
-      <c r="K573" s="9"/>
+      <c r="J573" s="8"/>
+      <c r="K573" s="8"/>
     </row>
     <row r="574" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J574" s="9"/>
-      <c r="K574" s="9"/>
+      <c r="J574" s="8"/>
+      <c r="K574" s="8"/>
     </row>
     <row r="575" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J575" s="9"/>
-      <c r="K575" s="9"/>
+      <c r="J575" s="8"/>
+      <c r="K575" s="8"/>
     </row>
     <row r="576" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J576" s="9"/>
-      <c r="K576" s="9"/>
+      <c r="J576" s="8"/>
+      <c r="K576" s="8"/>
     </row>
     <row r="577" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J577" s="9"/>
-      <c r="K577" s="9"/>
+      <c r="J577" s="8"/>
+      <c r="K577" s="8"/>
     </row>
     <row r="578" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J578" s="9"/>
-      <c r="K578" s="9"/>
+      <c r="J578" s="8"/>
+      <c r="K578" s="8"/>
     </row>
     <row r="579" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J579" s="9"/>
-      <c r="K579" s="9"/>
+      <c r="J579" s="8"/>
+      <c r="K579" s="8"/>
     </row>
     <row r="580" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J580" s="9"/>
-      <c r="K580" s="9"/>
+      <c r="J580" s="8"/>
+      <c r="K580" s="8"/>
     </row>
     <row r="581" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J581" s="9"/>
-      <c r="K581" s="9"/>
+      <c r="J581" s="8"/>
+      <c r="K581" s="8"/>
     </row>
     <row r="582" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J582" s="9"/>
-      <c r="K582" s="9"/>
+      <c r="J582" s="8"/>
+      <c r="K582" s="8"/>
     </row>
     <row r="583" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J583" s="9"/>
-      <c r="K583" s="9"/>
+      <c r="J583" s="8"/>
+      <c r="K583" s="8"/>
     </row>
     <row r="584" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J584" s="9"/>
-      <c r="K584" s="9"/>
+      <c r="J584" s="8"/>
+      <c r="K584" s="8"/>
     </row>
     <row r="585" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J585" s="9"/>
-      <c r="K585" s="9"/>
+      <c r="J585" s="8"/>
+      <c r="K585" s="8"/>
     </row>
     <row r="586" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J586" s="9"/>
-      <c r="K586" s="9"/>
+      <c r="J586" s="8"/>
+      <c r="K586" s="8"/>
     </row>
     <row r="587" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J587" s="9"/>
-      <c r="K587" s="9"/>
+      <c r="J587" s="8"/>
+      <c r="K587" s="8"/>
     </row>
     <row r="588" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J588" s="9"/>
-      <c r="K588" s="9"/>
+      <c r="J588" s="8"/>
+      <c r="K588" s="8"/>
     </row>
     <row r="589" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J589" s="9"/>
-      <c r="K589" s="9"/>
+      <c r="J589" s="8"/>
+      <c r="K589" s="8"/>
     </row>
     <row r="590" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J590" s="9"/>
-      <c r="K590" s="9"/>
+      <c r="J590" s="8"/>
+      <c r="K590" s="8"/>
     </row>
     <row r="591" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J591" s="9"/>
-      <c r="K591" s="9"/>
+      <c r="J591" s="8"/>
+      <c r="K591" s="8"/>
     </row>
     <row r="592" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J592" s="9"/>
-      <c r="K592" s="9"/>
+      <c r="J592" s="8"/>
+      <c r="K592" s="8"/>
     </row>
     <row r="593" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J593" s="9"/>
-      <c r="K593" s="9"/>
+      <c r="J593" s="8"/>
+      <c r="K593" s="8"/>
     </row>
     <row r="594" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J594" s="9"/>
-      <c r="K594" s="9"/>
+      <c r="J594" s="8"/>
+      <c r="K594" s="8"/>
     </row>
     <row r="595" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J595" s="9"/>
-      <c r="K595" s="9"/>
+      <c r="J595" s="8"/>
+      <c r="K595" s="8"/>
     </row>
     <row r="596" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J596" s="9"/>
-      <c r="K596" s="9"/>
+      <c r="J596" s="8"/>
+      <c r="K596" s="8"/>
     </row>
     <row r="597" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J597" s="9"/>
-      <c r="K597" s="9"/>
+      <c r="J597" s="8"/>
+      <c r="K597" s="8"/>
     </row>
     <row r="598" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J598" s="9"/>
-      <c r="K598" s="9"/>
+      <c r="J598" s="8"/>
+      <c r="K598" s="8"/>
     </row>
     <row r="599" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J599" s="9"/>
-      <c r="K599" s="9"/>
+      <c r="J599" s="8"/>
+      <c r="K599" s="8"/>
     </row>
     <row r="600" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J600" s="9"/>
-      <c r="K600" s="9"/>
+      <c r="J600" s="8"/>
+      <c r="K600" s="8"/>
     </row>
     <row r="601" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J601" s="9"/>
-      <c r="K601" s="9"/>
+      <c r="J601" s="8"/>
+      <c r="K601" s="8"/>
     </row>
     <row r="602" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J602" s="9"/>
-      <c r="K602" s="9"/>
+      <c r="J602" s="8"/>
+      <c r="K602" s="8"/>
     </row>
     <row r="603" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J603" s="9"/>
-      <c r="K603" s="9"/>
+      <c r="J603" s="8"/>
+      <c r="K603" s="8"/>
     </row>
     <row r="604" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J604" s="9"/>
-      <c r="K604" s="9"/>
+      <c r="J604" s="8"/>
+      <c r="K604" s="8"/>
     </row>
     <row r="605" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J605" s="9"/>
-      <c r="K605" s="9"/>
+      <c r="J605" s="8"/>
+      <c r="K605" s="8"/>
     </row>
     <row r="606" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J606" s="9"/>
-      <c r="K606" s="9"/>
+      <c r="J606" s="8"/>
+      <c r="K606" s="8"/>
     </row>
     <row r="607" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J607" s="9"/>
-      <c r="K607" s="9"/>
+      <c r="J607" s="8"/>
+      <c r="K607" s="8"/>
     </row>
     <row r="608" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J608" s="9"/>
-      <c r="K608" s="9"/>
+      <c r="J608" s="8"/>
+      <c r="K608" s="8"/>
     </row>
     <row r="609" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J609" s="9"/>
-      <c r="K609" s="9"/>
+      <c r="J609" s="8"/>
+      <c r="K609" s="8"/>
     </row>
     <row r="610" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J610" s="9"/>
-      <c r="K610" s="9"/>
+      <c r="J610" s="8"/>
+      <c r="K610" s="8"/>
     </row>
     <row r="611" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J611" s="9"/>
-      <c r="K611" s="9"/>
+      <c r="J611" s="8"/>
+      <c r="K611" s="8"/>
     </row>
     <row r="612" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J612" s="9"/>
-      <c r="K612" s="9"/>
+      <c r="J612" s="8"/>
+      <c r="K612" s="8"/>
     </row>
     <row r="613" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J613" s="9"/>
-      <c r="K613" s="9"/>
+      <c r="J613" s="8"/>
+      <c r="K613" s="8"/>
     </row>
     <row r="614" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J614" s="9"/>
-      <c r="K614" s="9"/>
+      <c r="J614" s="8"/>
+      <c r="K614" s="8"/>
     </row>
     <row r="615" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J615" s="9"/>
-      <c r="K615" s="9"/>
+      <c r="J615" s="8"/>
+      <c r="K615" s="8"/>
     </row>
     <row r="616" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J616" s="9"/>
-      <c r="K616" s="9"/>
+      <c r="J616" s="8"/>
+      <c r="K616" s="8"/>
     </row>
     <row r="617" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J617" s="9"/>
-      <c r="K617" s="9"/>
+      <c r="J617" s="8"/>
+      <c r="K617" s="8"/>
     </row>
     <row r="618" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J618" s="9"/>
-      <c r="K618" s="9"/>
+      <c r="J618" s="8"/>
+      <c r="K618" s="8"/>
     </row>
     <row r="619" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J619" s="9"/>
-      <c r="K619" s="9"/>
+      <c r="J619" s="8"/>
+      <c r="K619" s="8"/>
     </row>
     <row r="620" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J620" s="9"/>
-      <c r="K620" s="9"/>
+      <c r="J620" s="8"/>
+      <c r="K620" s="8"/>
     </row>
     <row r="621" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J621" s="9"/>
-      <c r="K621" s="9"/>
+      <c r="J621" s="8"/>
+      <c r="K621" s="8"/>
     </row>
     <row r="622" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J622" s="9"/>
-      <c r="K622" s="9"/>
+      <c r="J622" s="8"/>
+      <c r="K622" s="8"/>
     </row>
     <row r="623" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J623" s="9"/>
-      <c r="K623" s="9"/>
+      <c r="J623" s="8"/>
+      <c r="K623" s="8"/>
     </row>
     <row r="624" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J624" s="9"/>
-      <c r="K624" s="9"/>
+      <c r="J624" s="8"/>
+      <c r="K624" s="8"/>
     </row>
     <row r="625" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J625" s="9"/>
-      <c r="K625" s="9"/>
+      <c r="J625" s="8"/>
+      <c r="K625" s="8"/>
     </row>
     <row r="626" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J626" s="9"/>
-      <c r="K626" s="9"/>
+      <c r="J626" s="8"/>
+      <c r="K626" s="8"/>
     </row>
     <row r="627" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J627" s="9"/>
-      <c r="K627" s="9"/>
+      <c r="J627" s="8"/>
+      <c r="K627" s="8"/>
     </row>
     <row r="628" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J628" s="9"/>
-      <c r="K628" s="9"/>
+      <c r="J628" s="8"/>
+      <c r="K628" s="8"/>
     </row>
     <row r="629" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J629" s="9"/>
-      <c r="K629" s="9"/>
+      <c r="J629" s="8"/>
+      <c r="K629" s="8"/>
     </row>
     <row r="630" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J630" s="9"/>
-      <c r="K630" s="9"/>
+      <c r="J630" s="8"/>
+      <c r="K630" s="8"/>
     </row>
     <row r="631" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J631" s="9"/>
-      <c r="K631" s="9"/>
+      <c r="J631" s="8"/>
+      <c r="K631" s="8"/>
     </row>
     <row r="632" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J632" s="9"/>
-      <c r="K632" s="9"/>
+      <c r="J632" s="8"/>
+      <c r="K632" s="8"/>
     </row>
     <row r="633" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J633" s="9"/>
-      <c r="K633" s="9"/>
+      <c r="J633" s="8"/>
+      <c r="K633" s="8"/>
     </row>
     <row r="634" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J634" s="9"/>
-      <c r="K634" s="9"/>
+      <c r="J634" s="8"/>
+      <c r="K634" s="8"/>
     </row>
     <row r="635" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J635" s="9"/>
-      <c r="K635" s="9"/>
+      <c r="J635" s="8"/>
+      <c r="K635" s="8"/>
     </row>
     <row r="636" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J636" s="9"/>
-      <c r="K636" s="9"/>
+      <c r="J636" s="8"/>
+      <c r="K636" s="8"/>
     </row>
     <row r="637" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J637" s="9"/>
-      <c r="K637" s="9"/>
+      <c r="J637" s="8"/>
+      <c r="K637" s="8"/>
     </row>
     <row r="638" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J638" s="9"/>
-      <c r="K638" s="9"/>
+      <c r="J638" s="8"/>
+      <c r="K638" s="8"/>
     </row>
     <row r="639" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J639" s="9"/>
-      <c r="K639" s="9"/>
+      <c r="J639" s="8"/>
+      <c r="K639" s="8"/>
     </row>
     <row r="640" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J640" s="9"/>
-      <c r="K640" s="9"/>
+      <c r="J640" s="8"/>
+      <c r="K640" s="8"/>
     </row>
     <row r="641" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J641" s="9"/>
-      <c r="K641" s="9"/>
+      <c r="J641" s="8"/>
+      <c r="K641" s="8"/>
     </row>
     <row r="642" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J642" s="9"/>
-      <c r="K642" s="9"/>
+      <c r="J642" s="8"/>
+      <c r="K642" s="8"/>
     </row>
     <row r="643" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J643" s="9"/>
-      <c r="K643" s="9"/>
+      <c r="J643" s="8"/>
+      <c r="K643" s="8"/>
     </row>
     <row r="644" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J644" s="9"/>
-      <c r="K644" s="9"/>
+      <c r="J644" s="8"/>
+      <c r="K644" s="8"/>
     </row>
     <row r="645" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J645" s="9"/>
-      <c r="K645" s="9"/>
+      <c r="J645" s="8"/>
+      <c r="K645" s="8"/>
     </row>
     <row r="646" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J646" s="9"/>
-      <c r="K646" s="9"/>
+      <c r="J646" s="8"/>
+      <c r="K646" s="8"/>
     </row>
     <row r="647" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J647" s="9"/>
-      <c r="K647" s="9"/>
+      <c r="J647" s="8"/>
+      <c r="K647" s="8"/>
     </row>
     <row r="648" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J648" s="9"/>
-      <c r="K648" s="9"/>
+      <c r="J648" s="8"/>
+      <c r="K648" s="8"/>
     </row>
     <row r="649" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J649" s="9"/>
-      <c r="K649" s="9"/>
+      <c r="J649" s="8"/>
+      <c r="K649" s="8"/>
     </row>
     <row r="650" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J650" s="9"/>
-      <c r="K650" s="9"/>
+      <c r="J650" s="8"/>
+      <c r="K650" s="8"/>
     </row>
     <row r="651" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J651" s="9"/>
-      <c r="K651" s="9"/>
+      <c r="J651" s="8"/>
+      <c r="K651" s="8"/>
     </row>
     <row r="652" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J652" s="9"/>
-      <c r="K652" s="9"/>
+      <c r="J652" s="8"/>
+      <c r="K652" s="8"/>
     </row>
     <row r="653" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J653" s="9"/>
-      <c r="K653" s="9"/>
+      <c r="J653" s="8"/>
+      <c r="K653" s="8"/>
     </row>
     <row r="654" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J654" s="9"/>
-      <c r="K654" s="9"/>
+      <c r="J654" s="8"/>
+      <c r="K654" s="8"/>
     </row>
     <row r="655" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J655" s="9"/>
-      <c r="K655" s="9"/>
+      <c r="J655" s="8"/>
+      <c r="K655" s="8"/>
     </row>
     <row r="656" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J656" s="9"/>
-      <c r="K656" s="9"/>
+      <c r="J656" s="8"/>
+      <c r="K656" s="8"/>
     </row>
     <row r="657" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J657" s="9"/>
-      <c r="K657" s="9"/>
+      <c r="J657" s="8"/>
+      <c r="K657" s="8"/>
     </row>
     <row r="658" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J658" s="9"/>
-      <c r="K658" s="9"/>
+      <c r="J658" s="8"/>
+      <c r="K658" s="8"/>
     </row>
     <row r="659" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J659" s="9"/>
-      <c r="K659" s="9"/>
+      <c r="J659" s="8"/>
+      <c r="K659" s="8"/>
     </row>
     <row r="660" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J660" s="9"/>
-      <c r="K660" s="9"/>
+      <c r="J660" s="8"/>
+      <c r="K660" s="8"/>
     </row>
     <row r="661" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J661" s="9"/>
-      <c r="K661" s="9"/>
+      <c r="J661" s="8"/>
+      <c r="K661" s="8"/>
     </row>
     <row r="662" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J662" s="9"/>
-      <c r="K662" s="9"/>
+      <c r="J662" s="8"/>
+      <c r="K662" s="8"/>
     </row>
     <row r="663" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J663" s="9"/>
-      <c r="K663" s="9"/>
+      <c r="J663" s="8"/>
+      <c r="K663" s="8"/>
     </row>
     <row r="664" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J664" s="9"/>
-      <c r="K664" s="9"/>
+      <c r="J664" s="8"/>
+      <c r="K664" s="8"/>
     </row>
     <row r="665" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J665" s="9"/>
-      <c r="K665" s="9"/>
+      <c r="J665" s="8"/>
+      <c r="K665" s="8"/>
     </row>
     <row r="666" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J666" s="9"/>
-      <c r="K666" s="9"/>
+      <c r="J666" s="8"/>
+      <c r="K666" s="8"/>
     </row>
     <row r="667" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J667" s="9"/>
-      <c r="K667" s="9"/>
+      <c r="J667" s="8"/>
+      <c r="K667" s="8"/>
     </row>
     <row r="668" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J668" s="9"/>
-      <c r="K668" s="9"/>
+      <c r="J668" s="8"/>
+      <c r="K668" s="8"/>
     </row>
     <row r="669" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J669" s="9"/>
-      <c r="K669" s="9"/>
+      <c r="J669" s="8"/>
+      <c r="K669" s="8"/>
     </row>
     <row r="670" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J670" s="9"/>
-      <c r="K670" s="9"/>
+      <c r="J670" s="8"/>
+      <c r="K670" s="8"/>
     </row>
     <row r="671" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J671" s="9"/>
-      <c r="K671" s="9"/>
+      <c r="J671" s="8"/>
+      <c r="K671" s="8"/>
     </row>
     <row r="672" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J672" s="9"/>
-      <c r="K672" s="9"/>
+      <c r="J672" s="8"/>
+      <c r="K672" s="8"/>
     </row>
     <row r="673" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J673" s="9"/>
-      <c r="K673" s="9"/>
+      <c r="J673" s="8"/>
+      <c r="K673" s="8"/>
     </row>
     <row r="674" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J674" s="9"/>
-      <c r="K674" s="9"/>
+      <c r="J674" s="8"/>
+      <c r="K674" s="8"/>
     </row>
     <row r="675" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J675" s="9"/>
-      <c r="K675" s="9"/>
+      <c r="J675" s="8"/>
+      <c r="K675" s="8"/>
     </row>
     <row r="676" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J676" s="9"/>
-      <c r="K676" s="9"/>
+      <c r="J676" s="8"/>
+      <c r="K676" s="8"/>
     </row>
     <row r="677" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J677" s="9"/>
-      <c r="K677" s="9"/>
+      <c r="J677" s="8"/>
+      <c r="K677" s="8"/>
     </row>
     <row r="678" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J678" s="9"/>
-      <c r="K678" s="9"/>
+      <c r="J678" s="8"/>
+      <c r="K678" s="8"/>
     </row>
     <row r="679" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J679" s="9"/>
-      <c r="K679" s="9"/>
+      <c r="J679" s="8"/>
+      <c r="K679" s="8"/>
     </row>
     <row r="680" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J680" s="9"/>
-      <c r="K680" s="9"/>
+      <c r="J680" s="8"/>
+      <c r="K680" s="8"/>
     </row>
     <row r="681" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J681" s="9"/>
-      <c r="K681" s="9"/>
+      <c r="J681" s="8"/>
+      <c r="K681" s="8"/>
     </row>
     <row r="682" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J682" s="9"/>
-      <c r="K682" s="9"/>
+      <c r="J682" s="8"/>
+      <c r="K682" s="8"/>
     </row>
     <row r="683" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J683" s="9"/>
-      <c r="K683" s="9"/>
+      <c r="J683" s="8"/>
+      <c r="K683" s="8"/>
     </row>
     <row r="684" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J684" s="9"/>
-      <c r="K684" s="9"/>
+      <c r="J684" s="8"/>
+      <c r="K684" s="8"/>
     </row>
     <row r="685" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J685" s="9"/>
-      <c r="K685" s="9"/>
+      <c r="J685" s="8"/>
+      <c r="K685" s="8"/>
     </row>
     <row r="686" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J686" s="9"/>
-      <c r="K686" s="9"/>
+      <c r="J686" s="8"/>
+      <c r="K686" s="8"/>
     </row>
     <row r="687" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J687" s="9"/>
-      <c r="K687" s="9"/>
+      <c r="J687" s="8"/>
+      <c r="K687" s="8"/>
     </row>
     <row r="688" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J688" s="9"/>
-      <c r="K688" s="9"/>
+      <c r="J688" s="8"/>
+      <c r="K688" s="8"/>
     </row>
     <row r="689" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J689" s="9"/>
-      <c r="K689" s="9"/>
+      <c r="J689" s="8"/>
+      <c r="K689" s="8"/>
     </row>
     <row r="690" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J690" s="9"/>
-      <c r="K690" s="9"/>
+      <c r="J690" s="8"/>
+      <c r="K690" s="8"/>
     </row>
     <row r="691" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J691" s="9"/>
-      <c r="K691" s="9"/>
+      <c r="J691" s="8"/>
+      <c r="K691" s="8"/>
     </row>
     <row r="692" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J692" s="9"/>
-      <c r="K692" s="9"/>
+      <c r="J692" s="8"/>
+      <c r="K692" s="8"/>
     </row>
     <row r="693" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J693" s="9"/>
-      <c r="K693" s="9"/>
+      <c r="J693" s="8"/>
+      <c r="K693" s="8"/>
     </row>
     <row r="694" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J694" s="9"/>
-      <c r="K694" s="9"/>
+      <c r="J694" s="8"/>
+      <c r="K694" s="8"/>
     </row>
     <row r="695" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J695" s="9"/>
-      <c r="K695" s="9"/>
+      <c r="J695" s="8"/>
+      <c r="K695" s="8"/>
     </row>
     <row r="696" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J696" s="9"/>
-      <c r="K696" s="9"/>
+      <c r="J696" s="8"/>
+      <c r="K696" s="8"/>
     </row>
     <row r="697" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J697" s="9"/>
-      <c r="K697" s="9"/>
+      <c r="J697" s="8"/>
+      <c r="K697" s="8"/>
     </row>
     <row r="698" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J698" s="9"/>
-      <c r="K698" s="9"/>
+      <c r="J698" s="8"/>
+      <c r="K698" s="8"/>
     </row>
     <row r="699" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J699" s="9"/>
-      <c r="K699" s="9"/>
+      <c r="J699" s="8"/>
+      <c r="K699" s="8"/>
     </row>
     <row r="700" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J700" s="9"/>
-      <c r="K700" s="9"/>
+      <c r="J700" s="8"/>
+      <c r="K700" s="8"/>
     </row>
     <row r="701" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J701" s="9"/>
-      <c r="K701" s="9"/>
+      <c r="J701" s="8"/>
+      <c r="K701" s="8"/>
     </row>
     <row r="702" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J702" s="9"/>
-      <c r="K702" s="9"/>
+      <c r="J702" s="8"/>
+      <c r="K702" s="8"/>
     </row>
     <row r="703" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J703" s="9"/>
-      <c r="K703" s="9"/>
+      <c r="J703" s="8"/>
+      <c r="K703" s="8"/>
     </row>
     <row r="704" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J704" s="9"/>
-      <c r="K704" s="9"/>
+      <c r="J704" s="8"/>
+      <c r="K704" s="8"/>
     </row>
     <row r="705" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J705" s="9"/>
-      <c r="K705" s="9"/>
+      <c r="J705" s="8"/>
+      <c r="K705" s="8"/>
     </row>
     <row r="706" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J706" s="9"/>
-      <c r="K706" s="9"/>
+      <c r="J706" s="8"/>
+      <c r="K706" s="8"/>
     </row>
     <row r="707" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J707" s="9"/>
-      <c r="K707" s="9"/>
+      <c r="J707" s="8"/>
+      <c r="K707" s="8"/>
     </row>
     <row r="708" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J708" s="9"/>
-      <c r="K708" s="9"/>
+      <c r="J708" s="8"/>
+      <c r="K708" s="8"/>
     </row>
     <row r="709" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J709" s="9"/>
-      <c r="K709" s="9"/>
+      <c r="J709" s="8"/>
+      <c r="K709" s="8"/>
     </row>
     <row r="710" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J710" s="9"/>
-      <c r="K710" s="9"/>
+      <c r="J710" s="8"/>
+      <c r="K710" s="8"/>
     </row>
     <row r="711" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J711" s="9"/>
-      <c r="K711" s="9"/>
+      <c r="J711" s="8"/>
+      <c r="K711" s="8"/>
     </row>
     <row r="712" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J712" s="9"/>
-      <c r="K712" s="9"/>
+      <c r="J712" s="8"/>
+      <c r="K712" s="8"/>
     </row>
     <row r="713" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J713" s="9"/>
-      <c r="K713" s="9"/>
+      <c r="J713" s="8"/>
+      <c r="K713" s="8"/>
     </row>
     <row r="714" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J714" s="9"/>
-      <c r="K714" s="9"/>
+      <c r="J714" s="8"/>
+      <c r="K714" s="8"/>
     </row>
     <row r="715" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J715" s="9"/>
-      <c r="K715" s="9"/>
+      <c r="J715" s="8"/>
+      <c r="K715" s="8"/>
     </row>
     <row r="716" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J716" s="9"/>
-      <c r="K716" s="9"/>
+      <c r="J716" s="8"/>
+      <c r="K716" s="8"/>
     </row>
     <row r="717" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J717" s="9"/>
-      <c r="K717" s="9"/>
+      <c r="J717" s="8"/>
+      <c r="K717" s="8"/>
     </row>
     <row r="718" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J718" s="9"/>
-      <c r="K718" s="9"/>
+      <c r="J718" s="8"/>
+      <c r="K718" s="8"/>
     </row>
     <row r="719" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J719" s="9"/>
-      <c r="K719" s="9"/>
+      <c r="J719" s="8"/>
+      <c r="K719" s="8"/>
     </row>
     <row r="720" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J720" s="9"/>
-      <c r="K720" s="9"/>
+      <c r="J720" s="8"/>
+      <c r="K720" s="8"/>
     </row>
     <row r="721" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J721" s="9"/>
-      <c r="K721" s="9"/>
+      <c r="J721" s="8"/>
+      <c r="K721" s="8"/>
     </row>
     <row r="722" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J722" s="9"/>
-      <c r="K722" s="9"/>
+      <c r="J722" s="8"/>
+      <c r="K722" s="8"/>
     </row>
     <row r="723" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J723" s="9"/>
-      <c r="K723" s="9"/>
+      <c r="J723" s="8"/>
+      <c r="K723" s="8"/>
     </row>
     <row r="724" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J724" s="9"/>
-      <c r="K724" s="9"/>
+      <c r="J724" s="8"/>
+      <c r="K724" s="8"/>
     </row>
     <row r="725" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J725" s="9"/>
-      <c r="K725" s="9"/>
+      <c r="J725" s="8"/>
+      <c r="K725" s="8"/>
     </row>
     <row r="726" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J726" s="9"/>
-      <c r="K726" s="9"/>
+      <c r="J726" s="8"/>
+      <c r="K726" s="8"/>
     </row>
     <row r="727" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J727" s="9"/>
-      <c r="K727" s="9"/>
+      <c r="J727" s="8"/>
+      <c r="K727" s="8"/>
     </row>
     <row r="728" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J728" s="9"/>
-      <c r="K728" s="9"/>
+      <c r="J728" s="8"/>
+      <c r="K728" s="8"/>
     </row>
     <row r="729" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J729" s="9"/>
-      <c r="K729" s="9"/>
+      <c r="J729" s="8"/>
+      <c r="K729" s="8"/>
     </row>
     <row r="730" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J730" s="9"/>
-      <c r="K730" s="9"/>
+      <c r="J730" s="8"/>
+      <c r="K730" s="8"/>
     </row>
     <row r="731" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J731" s="9"/>
-      <c r="K731" s="9"/>
+      <c r="J731" s="8"/>
+      <c r="K731" s="8"/>
     </row>
     <row r="732" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J732" s="9"/>
-      <c r="K732" s="9"/>
+      <c r="J732" s="8"/>
+      <c r="K732" s="8"/>
     </row>
     <row r="733" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J733" s="9"/>
-      <c r="K733" s="9"/>
+      <c r="J733" s="8"/>
+      <c r="K733" s="8"/>
     </row>
     <row r="734" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J734" s="9"/>
-      <c r="K734" s="9"/>
+      <c r="J734" s="8"/>
+      <c r="K734" s="8"/>
     </row>
     <row r="735" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J735" s="9"/>
-      <c r="K735" s="9"/>
+      <c r="J735" s="8"/>
+      <c r="K735" s="8"/>
     </row>
     <row r="736" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J736" s="9"/>
-      <c r="K736" s="9"/>
+      <c r="J736" s="8"/>
+      <c r="K736" s="8"/>
     </row>
     <row r="737" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J737" s="9"/>
-      <c r="K737" s="9"/>
+      <c r="J737" s="8"/>
+      <c r="K737" s="8"/>
     </row>
     <row r="738" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J738" s="9"/>
-      <c r="K738" s="9"/>
+      <c r="J738" s="8"/>
+      <c r="K738" s="8"/>
     </row>
     <row r="739" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J739" s="9"/>
-      <c r="K739" s="9"/>
+      <c r="J739" s="8"/>
+      <c r="K739" s="8"/>
     </row>
     <row r="740" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J740" s="9"/>
-      <c r="K740" s="9"/>
+      <c r="J740" s="8"/>
+      <c r="K740" s="8"/>
     </row>
     <row r="741" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J741" s="9"/>
-      <c r="K741" s="9"/>
+      <c r="J741" s="8"/>
+      <c r="K741" s="8"/>
     </row>
     <row r="742" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J742" s="9"/>
-      <c r="K742" s="9"/>
+      <c r="J742" s="8"/>
+      <c r="K742" s="8"/>
     </row>
     <row r="743" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J743" s="9"/>
-      <c r="K743" s="9"/>
+      <c r="J743" s="8"/>
+      <c r="K743" s="8"/>
     </row>
     <row r="744" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J744" s="9"/>
-      <c r="K744" s="9"/>
+      <c r="J744" s="8"/>
+      <c r="K744" s="8"/>
     </row>
     <row r="745" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J745" s="9"/>
-      <c r="K745" s="9"/>
+      <c r="J745" s="8"/>
+      <c r="K745" s="8"/>
     </row>
     <row r="746" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J746" s="9"/>
-      <c r="K746" s="9"/>
+      <c r="J746" s="8"/>
+      <c r="K746" s="8"/>
     </row>
     <row r="747" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J747" s="9"/>
-      <c r="K747" s="9"/>
+      <c r="J747" s="8"/>
+      <c r="K747" s="8"/>
     </row>
     <row r="748" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J748" s="9"/>
-      <c r="K748" s="9"/>
+      <c r="J748" s="8"/>
+      <c r="K748" s="8"/>
     </row>
     <row r="749" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J749" s="9"/>
-      <c r="K749" s="9"/>
+      <c r="J749" s="8"/>
+      <c r="K749" s="8"/>
     </row>
     <row r="750" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J750" s="9"/>
-      <c r="K750" s="9"/>
+      <c r="J750" s="8"/>
+      <c r="K750" s="8"/>
     </row>
     <row r="751" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J751" s="9"/>
-      <c r="K751" s="9"/>
+      <c r="J751" s="8"/>
+      <c r="K751" s="8"/>
     </row>
     <row r="752" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J752" s="9"/>
-      <c r="K752" s="9"/>
+      <c r="J752" s="8"/>
+      <c r="K752" s="8"/>
     </row>
     <row r="753" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J753" s="9"/>
-      <c r="K753" s="9"/>
+      <c r="J753" s="8"/>
+      <c r="K753" s="8"/>
     </row>
     <row r="754" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J754" s="9"/>
-      <c r="K754" s="9"/>
+      <c r="J754" s="8"/>
+      <c r="K754" s="8"/>
     </row>
     <row r="755" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J755" s="9"/>
-      <c r="K755" s="9"/>
+      <c r="J755" s="8"/>
+      <c r="K755" s="8"/>
     </row>
     <row r="756" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J756" s="9"/>
-      <c r="K756" s="9"/>
+      <c r="J756" s="8"/>
+      <c r="K756" s="8"/>
     </row>
     <row r="757" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J757" s="9"/>
-      <c r="K757" s="9"/>
+      <c r="J757" s="8"/>
+      <c r="K757" s="8"/>
     </row>
     <row r="758" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J758" s="9"/>
-      <c r="K758" s="9"/>
+      <c r="J758" s="8"/>
+      <c r="K758" s="8"/>
     </row>
     <row r="759" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J759" s="9"/>
-      <c r="K759" s="9"/>
+      <c r="J759" s="8"/>
+      <c r="K759" s="8"/>
     </row>
     <row r="760" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J760" s="9"/>
-      <c r="K760" s="9"/>
+      <c r="J760" s="8"/>
+      <c r="K760" s="8"/>
     </row>
     <row r="761" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J761" s="9"/>
-      <c r="K761" s="9"/>
+      <c r="J761" s="8"/>
+      <c r="K761" s="8"/>
     </row>
     <row r="762" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J762" s="9"/>
-      <c r="K762" s="9"/>
+      <c r="J762" s="8"/>
+      <c r="K762" s="8"/>
     </row>
     <row r="763" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J763" s="9"/>
-      <c r="K763" s="9"/>
+      <c r="J763" s="8"/>
+      <c r="K763" s="8"/>
     </row>
     <row r="764" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J764" s="9"/>
-      <c r="K764" s="9"/>
+      <c r="J764" s="8"/>
+      <c r="K764" s="8"/>
     </row>
     <row r="765" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J765" s="9"/>
-      <c r="K765" s="9"/>
+      <c r="J765" s="8"/>
+      <c r="K765" s="8"/>
     </row>
     <row r="766" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J766" s="9"/>
-      <c r="K766" s="9"/>
+      <c r="J766" s="8"/>
+      <c r="K766" s="8"/>
     </row>
     <row r="767" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J767" s="9"/>
-      <c r="K767" s="9"/>
+      <c r="J767" s="8"/>
+      <c r="K767" s="8"/>
     </row>
     <row r="768" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J768" s="9"/>
-      <c r="K768" s="9"/>
+      <c r="J768" s="8"/>
+      <c r="K768" s="8"/>
     </row>
     <row r="769" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J769" s="9"/>
-      <c r="K769" s="9"/>
+      <c r="J769" s="8"/>
+      <c r="K769" s="8"/>
     </row>
     <row r="770" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J770" s="9"/>
-      <c r="K770" s="9"/>
+      <c r="J770" s="8"/>
+      <c r="K770" s="8"/>
     </row>
     <row r="771" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J771" s="9"/>
-      <c r="K771" s="9"/>
+      <c r="J771" s="8"/>
+      <c r="K771" s="8"/>
     </row>
     <row r="772" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J772" s="9"/>
-      <c r="K772" s="9"/>
+      <c r="J772" s="8"/>
+      <c r="K772" s="8"/>
     </row>
     <row r="773" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J773" s="9"/>
-      <c r="K773" s="9"/>
+      <c r="J773" s="8"/>
+      <c r="K773" s="8"/>
     </row>
     <row r="774" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J774" s="9"/>
-      <c r="K774" s="9"/>
+      <c r="J774" s="8"/>
+      <c r="K774" s="8"/>
     </row>
     <row r="775" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J775" s="9"/>
-      <c r="K775" s="9"/>
+      <c r="J775" s="8"/>
+      <c r="K775" s="8"/>
     </row>
     <row r="776" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J776" s="9"/>
-      <c r="K776" s="9"/>
+      <c r="J776" s="8"/>
+      <c r="K776" s="8"/>
     </row>
     <row r="777" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J777" s="9"/>
-      <c r="K777" s="9"/>
+      <c r="J777" s="8"/>
+      <c r="K777" s="8"/>
     </row>
     <row r="778" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J778" s="9"/>
-      <c r="K778" s="9"/>
+      <c r="J778" s="8"/>
+      <c r="K778" s="8"/>
     </row>
     <row r="779" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J779" s="9"/>
-      <c r="K779" s="9"/>
+      <c r="J779" s="8"/>
+      <c r="K779" s="8"/>
     </row>
     <row r="780" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J780" s="9"/>
-      <c r="K780" s="9"/>
+      <c r="J780" s="8"/>
+      <c r="K780" s="8"/>
     </row>
     <row r="781" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J781" s="9"/>
-      <c r="K781" s="9"/>
+      <c r="J781" s="8"/>
+      <c r="K781" s="8"/>
     </row>
     <row r="782" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J782" s="9"/>
-      <c r="K782" s="9"/>
+      <c r="J782" s="8"/>
+      <c r="K782" s="8"/>
     </row>
     <row r="783" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J783" s="9"/>
-      <c r="K783" s="9"/>
+      <c r="J783" s="8"/>
+      <c r="K783" s="8"/>
     </row>
     <row r="784" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J784" s="9"/>
-      <c r="K784" s="9"/>
+      <c r="J784" s="8"/>
+      <c r="K784" s="8"/>
     </row>
     <row r="785" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J785" s="9"/>
-      <c r="K785" s="9"/>
+      <c r="J785" s="8"/>
+      <c r="K785" s="8"/>
     </row>
     <row r="786" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J786" s="9"/>
-      <c r="K786" s="9"/>
+      <c r="J786" s="8"/>
+      <c r="K786" s="8"/>
     </row>
     <row r="787" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J787" s="9"/>
-      <c r="K787" s="9"/>
+      <c r="J787" s="8"/>
+      <c r="K787" s="8"/>
     </row>
     <row r="788" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J788" s="9"/>
-      <c r="K788" s="9"/>
+      <c r="J788" s="8"/>
+      <c r="K788" s="8"/>
     </row>
     <row r="789" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J789" s="9"/>
-      <c r="K789" s="9"/>
+      <c r="J789" s="8"/>
+      <c r="K789" s="8"/>
     </row>
     <row r="790" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J790" s="9"/>
-      <c r="K790" s="9"/>
+      <c r="J790" s="8"/>
+      <c r="K790" s="8"/>
     </row>
     <row r="791" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J791" s="9"/>
-      <c r="K791" s="9"/>
+      <c r="J791" s="8"/>
+      <c r="K791" s="8"/>
     </row>
     <row r="792" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J792" s="9"/>
-      <c r="K792" s="9"/>
+      <c r="J792" s="8"/>
+      <c r="K792" s="8"/>
     </row>
     <row r="793" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J793" s="9"/>
-      <c r="K793" s="9"/>
+      <c r="J793" s="8"/>
+      <c r="K793" s="8"/>
     </row>
     <row r="794" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J794" s="9"/>
-      <c r="K794" s="9"/>
+      <c r="J794" s="8"/>
+      <c r="K794" s="8"/>
     </row>
     <row r="795" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J795" s="9"/>
-      <c r="K795" s="9"/>
+      <c r="J795" s="8"/>
+      <c r="K795" s="8"/>
     </row>
     <row r="796" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J796" s="9"/>
-      <c r="K796" s="9"/>
+      <c r="J796" s="8"/>
+      <c r="K796" s="8"/>
     </row>
     <row r="797" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J797" s="9"/>
-      <c r="K797" s="9"/>
+      <c r="J797" s="8"/>
+      <c r="K797" s="8"/>
     </row>
     <row r="798" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J798" s="9"/>
-      <c r="K798" s="9"/>
+      <c r="J798" s="8"/>
+      <c r="K798" s="8"/>
     </row>
     <row r="799" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J799" s="9"/>
-      <c r="K799" s="9"/>
+      <c r="J799" s="8"/>
+      <c r="K799" s="8"/>
     </row>
     <row r="800" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J800" s="9"/>
-      <c r="K800" s="9"/>
+      <c r="J800" s="8"/>
+      <c r="K800" s="8"/>
     </row>
     <row r="801" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J801" s="9"/>
-      <c r="K801" s="9"/>
+      <c r="J801" s="8"/>
+      <c r="K801" s="8"/>
     </row>
     <row r="802" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J802" s="9"/>
-      <c r="K802" s="9"/>
+      <c r="J802" s="8"/>
+      <c r="K802" s="8"/>
     </row>
     <row r="803" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J803" s="9"/>
-      <c r="K803" s="9"/>
+      <c r="J803" s="8"/>
+      <c r="K803" s="8"/>
     </row>
     <row r="804" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J804" s="9"/>
-      <c r="K804" s="9"/>
+      <c r="J804" s="8"/>
+      <c r="K804" s="8"/>
     </row>
     <row r="805" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J805" s="9"/>
-      <c r="K805" s="9"/>
+      <c r="J805" s="8"/>
+      <c r="K805" s="8"/>
     </row>
     <row r="806" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J806" s="9"/>
-      <c r="K806" s="9"/>
+      <c r="J806" s="8"/>
+      <c r="K806" s="8"/>
     </row>
     <row r="807" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J807" s="9"/>
-      <c r="K807" s="9"/>
+      <c r="J807" s="8"/>
+      <c r="K807" s="8"/>
     </row>
     <row r="808" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J808" s="9"/>
-      <c r="K808" s="9"/>
+      <c r="J808" s="8"/>
+      <c r="K808" s="8"/>
     </row>
     <row r="809" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J809" s="9"/>
-      <c r="K809" s="9"/>
+      <c r="J809" s="8"/>
+      <c r="K809" s="8"/>
     </row>
     <row r="810" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J810" s="9"/>
-      <c r="K810" s="9"/>
+      <c r="J810" s="8"/>
+      <c r="K810" s="8"/>
     </row>
     <row r="811" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J811" s="9"/>
-      <c r="K811" s="9"/>
+      <c r="J811" s="8"/>
+      <c r="K811" s="8"/>
     </row>
     <row r="812" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J812" s="9"/>
-      <c r="K812" s="9"/>
+      <c r="J812" s="8"/>
+      <c r="K812" s="8"/>
     </row>
     <row r="813" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J813" s="9"/>
-      <c r="K813" s="9"/>
+      <c r="J813" s="8"/>
+      <c r="K813" s="8"/>
     </row>
     <row r="814" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J814" s="9"/>
-      <c r="K814" s="9"/>
+      <c r="J814" s="8"/>
+      <c r="K814" s="8"/>
     </row>
     <row r="815" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J815" s="9"/>
-      <c r="K815" s="9"/>
+      <c r="J815" s="8"/>
+      <c r="K815" s="8"/>
     </row>
     <row r="816" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J816" s="9"/>
-      <c r="K816" s="9"/>
+      <c r="J816" s="8"/>
+      <c r="K816" s="8"/>
     </row>
     <row r="817" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J817" s="9"/>
-      <c r="K817" s="9"/>
+      <c r="J817" s="8"/>
+      <c r="K817" s="8"/>
     </row>
     <row r="818" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J818" s="9"/>
-      <c r="K818" s="9"/>
+      <c r="J818" s="8"/>
+      <c r="K818" s="8"/>
     </row>
     <row r="819" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J819" s="9"/>
-      <c r="K819" s="9"/>
+      <c r="J819" s="8"/>
+      <c r="K819" s="8"/>
     </row>
     <row r="820" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J820" s="9"/>
-      <c r="K820" s="9"/>
+      <c r="J820" s="8"/>
+      <c r="K820" s="8"/>
     </row>
     <row r="821" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J821" s="9"/>
-      <c r="K821" s="9"/>
+      <c r="J821" s="8"/>
+      <c r="K821" s="8"/>
     </row>
     <row r="822" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J822" s="9"/>
-      <c r="K822" s="9"/>
+      <c r="J822" s="8"/>
+      <c r="K822" s="8"/>
     </row>
     <row r="823" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J823" s="9"/>
-      <c r="K823" s="9"/>
+      <c r="J823" s="8"/>
+      <c r="K823" s="8"/>
     </row>
     <row r="824" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J824" s="9"/>
-      <c r="K824" s="9"/>
+      <c r="J824" s="8"/>
+      <c r="K824" s="8"/>
     </row>
     <row r="825" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J825" s="9"/>
-      <c r="K825" s="9"/>
+      <c r="J825" s="8"/>
+      <c r="K825" s="8"/>
     </row>
     <row r="826" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J826" s="9"/>
-      <c r="K826" s="9"/>
+      <c r="J826" s="8"/>
+      <c r="K826" s="8"/>
     </row>
     <row r="827" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J827" s="9"/>
-      <c r="K827" s="9"/>
+      <c r="J827" s="8"/>
+      <c r="K827" s="8"/>
     </row>
     <row r="828" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J828" s="9"/>
-      <c r="K828" s="9"/>
+      <c r="J828" s="8"/>
+      <c r="K828" s="8"/>
     </row>
     <row r="829" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J829" s="9"/>
-      <c r="K829" s="9"/>
+      <c r="J829" s="8"/>
+      <c r="K829" s="8"/>
     </row>
     <row r="830" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J830" s="9"/>
-      <c r="K830" s="9"/>
+      <c r="J830" s="8"/>
+      <c r="K830" s="8"/>
     </row>
     <row r="831" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J831" s="9"/>
-      <c r="K831" s="9"/>
+      <c r="J831" s="8"/>
+      <c r="K831" s="8"/>
     </row>
     <row r="832" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J832" s="9"/>
-      <c r="K832" s="9"/>
+      <c r="J832" s="8"/>
+      <c r="K832" s="8"/>
     </row>
     <row r="833" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J833" s="9"/>
-      <c r="K833" s="9"/>
+      <c r="J833" s="8"/>
+      <c r="K833" s="8"/>
     </row>
     <row r="834" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J834" s="9"/>
-      <c r="K834" s="9"/>
+      <c r="J834" s="8"/>
+      <c r="K834" s="8"/>
     </row>
     <row r="835" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J835" s="9"/>
-      <c r="K835" s="9"/>
+      <c r="J835" s="8"/>
+      <c r="K835" s="8"/>
     </row>
     <row r="836" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J836" s="9"/>
-      <c r="K836" s="9"/>
+      <c r="J836" s="8"/>
+      <c r="K836" s="8"/>
     </row>
     <row r="837" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J837" s="9"/>
-      <c r="K837" s="9"/>
+      <c r="J837" s="8"/>
+      <c r="K837" s="8"/>
     </row>
     <row r="838" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J838" s="9"/>
-      <c r="K838" s="9"/>
+      <c r="J838" s="8"/>
+      <c r="K838" s="8"/>
     </row>
     <row r="839" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J839" s="9"/>
-      <c r="K839" s="9"/>
+      <c r="J839" s="8"/>
+      <c r="K839" s="8"/>
     </row>
     <row r="840" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J840" s="9"/>
-      <c r="K840" s="9"/>
+      <c r="J840" s="8"/>
+      <c r="K840" s="8"/>
     </row>
     <row r="841" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J841" s="9"/>
-      <c r="K841" s="9"/>
+      <c r="J841" s="8"/>
+      <c r="K841" s="8"/>
     </row>
     <row r="842" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J842" s="9"/>
-      <c r="K842" s="9"/>
+      <c r="J842" s="8"/>
+      <c r="K842" s="8"/>
     </row>
     <row r="843" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J843" s="9"/>
-      <c r="K843" s="9"/>
+      <c r="J843" s="8"/>
+      <c r="K843" s="8"/>
     </row>
     <row r="844" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J844" s="9"/>
-      <c r="K844" s="9"/>
+      <c r="J844" s="8"/>
+      <c r="K844" s="8"/>
     </row>
     <row r="845" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J845" s="9"/>
-      <c r="K845" s="9"/>
+      <c r="J845" s="8"/>
+      <c r="K845" s="8"/>
     </row>
     <row r="846" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J846" s="9"/>
-      <c r="K846" s="9"/>
+      <c r="J846" s="8"/>
+      <c r="K846" s="8"/>
     </row>
     <row r="847" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J847" s="9"/>
-      <c r="K847" s="9"/>
+      <c r="J847" s="8"/>
+      <c r="K847" s="8"/>
     </row>
     <row r="848" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J848" s="9"/>
-      <c r="K848" s="9"/>
+      <c r="J848" s="8"/>
+      <c r="K848" s="8"/>
     </row>
     <row r="849" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J849" s="9"/>
-      <c r="K849" s="9"/>
+      <c r="J849" s="8"/>
+      <c r="K849" s="8"/>
     </row>
     <row r="850" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J850" s="9"/>
-      <c r="K850" s="9"/>
+      <c r="J850" s="8"/>
+      <c r="K850" s="8"/>
     </row>
     <row r="851" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J851" s="9"/>
-      <c r="K851" s="9"/>
+      <c r="J851" s="8"/>
+      <c r="K851" s="8"/>
     </row>
     <row r="852" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J852" s="9"/>
-      <c r="K852" s="9"/>
+      <c r="J852" s="8"/>
+      <c r="K852" s="8"/>
     </row>
     <row r="853" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J853" s="9"/>
-      <c r="K853" s="9"/>
+      <c r="J853" s="8"/>
+      <c r="K853" s="8"/>
     </row>
     <row r="854" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J854" s="9"/>
-      <c r="K854" s="9"/>
+      <c r="J854" s="8"/>
+      <c r="K854" s="8"/>
     </row>
     <row r="855" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J855" s="9"/>
-      <c r="K855" s="9"/>
+      <c r="J855" s="8"/>
+      <c r="K855" s="8"/>
     </row>
     <row r="856" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J856" s="9"/>
-      <c r="K856" s="9"/>
+      <c r="J856" s="8"/>
+      <c r="K856" s="8"/>
     </row>
     <row r="857" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J857" s="9"/>
-      <c r="K857" s="9"/>
+      <c r="J857" s="8"/>
+      <c r="K857" s="8"/>
     </row>
     <row r="858" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J858" s="9"/>
-      <c r="K858" s="9"/>
+      <c r="J858" s="8"/>
+      <c r="K858" s="8"/>
     </row>
     <row r="859" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J859" s="9"/>
-      <c r="K859" s="9"/>
+      <c r="J859" s="8"/>
+      <c r="K859" s="8"/>
     </row>
     <row r="860" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J860" s="9"/>
-      <c r="K860" s="9"/>
+      <c r="J860" s="8"/>
+      <c r="K860" s="8"/>
     </row>
     <row r="861" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J861" s="9"/>
-      <c r="K861" s="9"/>
+      <c r="J861" s="8"/>
+      <c r="K861" s="8"/>
     </row>
     <row r="862" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J862" s="9"/>
-      <c r="K862" s="9"/>
+      <c r="J862" s="8"/>
+      <c r="K862" s="8"/>
     </row>
     <row r="863" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J863" s="9"/>
-      <c r="K863" s="9"/>
+      <c r="J863" s="8"/>
+      <c r="K863" s="8"/>
     </row>
     <row r="864" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J864" s="9"/>
-      <c r="K864" s="9"/>
+      <c r="J864" s="8"/>
+      <c r="K864" s="8"/>
     </row>
     <row r="865" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J865" s="9"/>
-      <c r="K865" s="9"/>
+      <c r="J865" s="8"/>
+      <c r="K865" s="8"/>
     </row>
     <row r="866" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J866" s="9"/>
-      <c r="K866" s="9"/>
+      <c r="J866" s="8"/>
+      <c r="K866" s="8"/>
     </row>
     <row r="867" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J867" s="9"/>
-      <c r="K867" s="9"/>
+      <c r="J867" s="8"/>
+      <c r="K867" s="8"/>
     </row>
     <row r="868" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J868" s="9"/>
-      <c r="K868" s="9"/>
+      <c r="J868" s="8"/>
+      <c r="K868" s="8"/>
     </row>
     <row r="869" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J869" s="9"/>
-      <c r="K869" s="9"/>
+      <c r="J869" s="8"/>
+      <c r="K869" s="8"/>
     </row>
     <row r="870" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J870" s="9"/>
-      <c r="K870" s="9"/>
+      <c r="J870" s="8"/>
+      <c r="K870" s="8"/>
     </row>
     <row r="871" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J871" s="9"/>
-      <c r="K871" s="9"/>
+      <c r="J871" s="8"/>
+      <c r="K871" s="8"/>
     </row>
     <row r="872" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J872" s="9"/>
-      <c r="K872" s="9"/>
+      <c r="J872" s="8"/>
+      <c r="K872" s="8"/>
     </row>
     <row r="873" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J873" s="9"/>
-      <c r="K873" s="9"/>
+      <c r="J873" s="8"/>
+      <c r="K873" s="8"/>
     </row>
     <row r="874" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J874" s="9"/>
-      <c r="K874" s="9"/>
+      <c r="J874" s="8"/>
+      <c r="K874" s="8"/>
     </row>
     <row r="875" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J875" s="9"/>
-      <c r="K875" s="9"/>
+      <c r="J875" s="8"/>
+      <c r="K875" s="8"/>
     </row>
     <row r="876" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J876" s="9"/>
-      <c r="K876" s="9"/>
+      <c r="J876" s="8"/>
+      <c r="K876" s="8"/>
     </row>
     <row r="877" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J877" s="9"/>
-      <c r="K877" s="9"/>
+      <c r="J877" s="8"/>
+      <c r="K877" s="8"/>
     </row>
     <row r="878" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J878" s="9"/>
-      <c r="K878" s="9"/>
+      <c r="J878" s="8"/>
+      <c r="K878" s="8"/>
     </row>
     <row r="879" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J879" s="9"/>
-      <c r="K879" s="9"/>
+      <c r="J879" s="8"/>
+      <c r="K879" s="8"/>
     </row>
     <row r="880" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J880" s="9"/>
-      <c r="K880" s="9"/>
+      <c r="J880" s="8"/>
+      <c r="K880" s="8"/>
     </row>
     <row r="881" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J881" s="9"/>
-      <c r="K881" s="9"/>
+      <c r="J881" s="8"/>
+      <c r="K881" s="8"/>
     </row>
     <row r="882" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J882" s="9"/>
-      <c r="K882" s="9"/>
+      <c r="J882" s="8"/>
+      <c r="K882" s="8"/>
     </row>
     <row r="883" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J883" s="9"/>
-      <c r="K883" s="9"/>
+      <c r="J883" s="8"/>
+      <c r="K883" s="8"/>
     </row>
     <row r="884" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J884" s="9"/>
-      <c r="K884" s="9"/>
+      <c r="J884" s="8"/>
+      <c r="K884" s="8"/>
     </row>
     <row r="885" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J885" s="9"/>
-      <c r="K885" s="9"/>
+      <c r="J885" s="8"/>
+      <c r="K885" s="8"/>
     </row>
     <row r="886" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J886" s="9"/>
-      <c r="K886" s="9"/>
+      <c r="J886" s="8"/>
+      <c r="K886" s="8"/>
     </row>
     <row r="887" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J887" s="9"/>
-      <c r="K887" s="9"/>
+      <c r="J887" s="8"/>
+      <c r="K887" s="8"/>
     </row>
     <row r="888" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J888" s="9"/>
-      <c r="K888" s="9"/>
+      <c r="J888" s="8"/>
+      <c r="K888" s="8"/>
     </row>
     <row r="889" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J889" s="9"/>
-      <c r="K889" s="9"/>
+      <c r="J889" s="8"/>
+      <c r="K889" s="8"/>
     </row>
     <row r="890" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J890" s="9"/>
-      <c r="K890" s="9"/>
+      <c r="J890" s="8"/>
+      <c r="K890" s="8"/>
     </row>
     <row r="891" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J891" s="9"/>
-      <c r="K891" s="9"/>
+      <c r="J891" s="8"/>
+      <c r="K891" s="8"/>
     </row>
     <row r="892" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J892" s="9"/>
-      <c r="K892" s="9"/>
+      <c r="J892" s="8"/>
+      <c r="K892" s="8"/>
     </row>
     <row r="893" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J893" s="9"/>
-      <c r="K893" s="9"/>
+      <c r="J893" s="8"/>
+      <c r="K893" s="8"/>
     </row>
     <row r="894" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J894" s="9"/>
-      <c r="K894" s="9"/>
+      <c r="J894" s="8"/>
+      <c r="K894" s="8"/>
     </row>
     <row r="895" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J895" s="9"/>
-      <c r="K895" s="9"/>
+      <c r="J895" s="8"/>
+      <c r="K895" s="8"/>
     </row>
     <row r="896" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J896" s="9"/>
-      <c r="K896" s="9"/>
+      <c r="J896" s="8"/>
+      <c r="K896" s="8"/>
     </row>
     <row r="897" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J897" s="9"/>
-      <c r="K897" s="9"/>
+      <c r="J897" s="8"/>
+      <c r="K897" s="8"/>
     </row>
     <row r="898" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J898" s="9"/>
-      <c r="K898" s="9"/>
+      <c r="J898" s="8"/>
+      <c r="K898" s="8"/>
     </row>
     <row r="899" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J899" s="9"/>
-      <c r="K899" s="9"/>
+      <c r="J899" s="8"/>
+      <c r="K899" s="8"/>
     </row>
     <row r="900" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J900" s="9"/>
-      <c r="K900" s="9"/>
+      <c r="J900" s="8"/>
+      <c r="K900" s="8"/>
     </row>
     <row r="901" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J901" s="9"/>
-      <c r="K901" s="9"/>
+      <c r="J901" s="8"/>
+      <c r="K901" s="8"/>
     </row>
     <row r="902" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J902" s="9"/>
-      <c r="K902" s="9"/>
+      <c r="J902" s="8"/>
+      <c r="K902" s="8"/>
     </row>
     <row r="903" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J903" s="9"/>
-      <c r="K903" s="9"/>
+      <c r="J903" s="8"/>
+      <c r="K903" s="8"/>
     </row>
     <row r="904" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J904" s="9"/>
-      <c r="K904" s="9"/>
+      <c r="J904" s="8"/>
+      <c r="K904" s="8"/>
     </row>
     <row r="905" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J905" s="9"/>
-      <c r="K905" s="9"/>
+      <c r="J905" s="8"/>
+      <c r="K905" s="8"/>
     </row>
     <row r="906" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J906" s="9"/>
-      <c r="K906" s="9"/>
+      <c r="J906" s="8"/>
+      <c r="K906" s="8"/>
     </row>
     <row r="907" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J907" s="9"/>
-      <c r="K907" s="9"/>
+      <c r="J907" s="8"/>
+      <c r="K907" s="8"/>
     </row>
     <row r="908" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J908" s="9"/>
-      <c r="K908" s="9"/>
+      <c r="J908" s="8"/>
+      <c r="K908" s="8"/>
     </row>
     <row r="909" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J909" s="9"/>
-      <c r="K909" s="9"/>
+      <c r="J909" s="8"/>
+      <c r="K909" s="8"/>
     </row>
     <row r="910" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J910" s="9"/>
-      <c r="K910" s="9"/>
+      <c r="J910" s="8"/>
+      <c r="K910" s="8"/>
     </row>
     <row r="911" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J911" s="9"/>
-      <c r="K911" s="9"/>
+      <c r="J911" s="8"/>
+      <c r="K911" s="8"/>
     </row>
     <row r="912" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J912" s="9"/>
-      <c r="K912" s="9"/>
+      <c r="J912" s="8"/>
+      <c r="K912" s="8"/>
     </row>
     <row r="913" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J913" s="9"/>
-      <c r="K913" s="9"/>
+      <c r="J913" s="8"/>
+      <c r="K913" s="8"/>
     </row>
     <row r="914" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J914" s="9"/>
-      <c r="K914" s="9"/>
+      <c r="J914" s="8"/>
+      <c r="K914" s="8"/>
     </row>
     <row r="915" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J915" s="9"/>
-      <c r="K915" s="9"/>
+      <c r="J915" s="8"/>
+      <c r="K915" s="8"/>
     </row>
     <row r="916" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J916" s="9"/>
-      <c r="K916" s="9"/>
+      <c r="J916" s="8"/>
+      <c r="K916" s="8"/>
     </row>
     <row r="917" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J917" s="9"/>
-      <c r="K917" s="9"/>
+      <c r="J917" s="8"/>
+      <c r="K917" s="8"/>
     </row>
     <row r="918" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J918" s="9"/>
-      <c r="K918" s="9"/>
+      <c r="J918" s="8"/>
+      <c r="K918" s="8"/>
     </row>
     <row r="919" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J919" s="9"/>
-      <c r="K919" s="9"/>
+      <c r="J919" s="8"/>
+      <c r="K919" s="8"/>
     </row>
     <row r="920" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J920" s="9"/>
-      <c r="K920" s="9"/>
+      <c r="J920" s="8"/>
+      <c r="K920" s="8"/>
     </row>
     <row r="921" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J921" s="9"/>
-      <c r="K921" s="9"/>
+      <c r="J921" s="8"/>
+      <c r="K921" s="8"/>
     </row>
     <row r="922" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J922" s="9"/>
-      <c r="K922" s="9"/>
+      <c r="J922" s="8"/>
+      <c r="K922" s="8"/>
     </row>
     <row r="923" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J923" s="9"/>
-      <c r="K923" s="9"/>
+      <c r="J923" s="8"/>
+      <c r="K923" s="8"/>
     </row>
     <row r="924" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J924" s="9"/>
-      <c r="K924" s="9"/>
+      <c r="J924" s="8"/>
+      <c r="K924" s="8"/>
     </row>
     <row r="925" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J925" s="9"/>
-      <c r="K925" s="9"/>
+      <c r="J925" s="8"/>
+      <c r="K925" s="8"/>
     </row>
     <row r="926" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J926" s="9"/>
-      <c r="K926" s="9"/>
+      <c r="J926" s="8"/>
+      <c r="K926" s="8"/>
     </row>
     <row r="927" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J927" s="9"/>
-      <c r="K927" s="9"/>
+      <c r="J927" s="8"/>
+      <c r="K927" s="8"/>
     </row>
     <row r="928" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J928" s="9"/>
-      <c r="K928" s="9"/>
+      <c r="J928" s="8"/>
+      <c r="K928" s="8"/>
     </row>
     <row r="929" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J929" s="9"/>
-      <c r="K929" s="9"/>
+      <c r="J929" s="8"/>
+      <c r="K929" s="8"/>
     </row>
     <row r="930" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J930" s="9"/>
-      <c r="K930" s="9"/>
+      <c r="J930" s="8"/>
+      <c r="K930" s="8"/>
     </row>
     <row r="931" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J931" s="9"/>
-      <c r="K931" s="9"/>
+      <c r="J931" s="8"/>
+      <c r="K931" s="8"/>
     </row>
     <row r="932" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J932" s="9"/>
-      <c r="K932" s="9"/>
+      <c r="J932" s="8"/>
+      <c r="K932" s="8"/>
     </row>
     <row r="933" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J933" s="9"/>
-      <c r="K933" s="9"/>
+      <c r="J933" s="8"/>
+      <c r="K933" s="8"/>
     </row>
     <row r="934" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J934" s="9"/>
-      <c r="K934" s="9"/>
+      <c r="J934" s="8"/>
+      <c r="K934" s="8"/>
     </row>
     <row r="935" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J935" s="9"/>
-      <c r="K935" s="9"/>
+      <c r="J935" s="8"/>
+      <c r="K935" s="8"/>
     </row>
     <row r="936" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J936" s="9"/>
-      <c r="K936" s="9"/>
+      <c r="J936" s="8"/>
+      <c r="K936" s="8"/>
     </row>
     <row r="937" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J937" s="9"/>
-      <c r="K937" s="9"/>
+      <c r="J937" s="8"/>
+      <c r="K937" s="8"/>
     </row>
     <row r="938" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J938" s="9"/>
-      <c r="K938" s="9"/>
+      <c r="J938" s="8"/>
+      <c r="K938" s="8"/>
     </row>
     <row r="939" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J939" s="9"/>
-      <c r="K939" s="9"/>
+      <c r="J939" s="8"/>
+      <c r="K939" s="8"/>
     </row>
     <row r="940" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J940" s="9"/>
-      <c r="K940" s="9"/>
+      <c r="J940" s="8"/>
+      <c r="K940" s="8"/>
     </row>
     <row r="941" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J941" s="9"/>
-      <c r="K941" s="9"/>
+      <c r="J941" s="8"/>
+      <c r="K941" s="8"/>
     </row>
     <row r="942" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J942" s="9"/>
-      <c r="K942" s="9"/>
+      <c r="J942" s="8"/>
+      <c r="K942" s="8"/>
     </row>
     <row r="943" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J943" s="9"/>
-      <c r="K943" s="9"/>
+      <c r="J943" s="8"/>
+      <c r="K943" s="8"/>
     </row>
     <row r="944" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J944" s="9"/>
-      <c r="K944" s="9"/>
+      <c r="J944" s="8"/>
+      <c r="K944" s="8"/>
     </row>
     <row r="945" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J945" s="9"/>
-      <c r="K945" s="9"/>
+      <c r="J945" s="8"/>
+      <c r="K945" s="8"/>
     </row>
     <row r="946" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J946" s="9"/>
-      <c r="K946" s="9"/>
+      <c r="J946" s="8"/>
+      <c r="K946" s="8"/>
     </row>
     <row r="947" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J947" s="9"/>
-      <c r="K947" s="9"/>
+      <c r="J947" s="8"/>
+      <c r="K947" s="8"/>
     </row>
     <row r="948" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J948" s="9"/>
-      <c r="K948" s="9"/>
+      <c r="J948" s="8"/>
+      <c r="K948" s="8"/>
     </row>
     <row r="949" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J949" s="9"/>
-      <c r="K949" s="9"/>
+      <c r="J949" s="8"/>
+      <c r="K949" s="8"/>
     </row>
     <row r="950" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J950" s="9"/>
-      <c r="K950" s="9"/>
+      <c r="J950" s="8"/>
+      <c r="K950" s="8"/>
     </row>
     <row r="951" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J951" s="9"/>
-      <c r="K951" s="9"/>
+      <c r="J951" s="8"/>
+      <c r="K951" s="8"/>
     </row>
     <row r="952" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J952" s="9"/>
-      <c r="K952" s="9"/>
+      <c r="J952" s="8"/>
+      <c r="K952" s="8"/>
     </row>
     <row r="953" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J953" s="9"/>
-      <c r="K953" s="9"/>
+      <c r="J953" s="8"/>
+      <c r="K953" s="8"/>
     </row>
     <row r="954" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J954" s="9"/>
-      <c r="K954" s="9"/>
+      <c r="J954" s="8"/>
+      <c r="K954" s="8"/>
     </row>
     <row r="955" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J955" s="9"/>
-      <c r="K955" s="9"/>
+      <c r="J955" s="8"/>
+      <c r="K955" s="8"/>
     </row>
     <row r="956" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J956" s="9"/>
-      <c r="K956" s="9"/>
+      <c r="J956" s="8"/>
+      <c r="K956" s="8"/>
     </row>
     <row r="957" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J957" s="9"/>
-      <c r="K957" s="9"/>
+      <c r="J957" s="8"/>
+      <c r="K957" s="8"/>
     </row>
     <row r="958" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J958" s="9"/>
-      <c r="K958" s="9"/>
+      <c r="J958" s="8"/>
+      <c r="K958" s="8"/>
     </row>
     <row r="959" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J959" s="9"/>
-      <c r="K959" s="9"/>
+      <c r="J959" s="8"/>
+      <c r="K959" s="8"/>
     </row>
     <row r="960" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J960" s="9"/>
-      <c r="K960" s="9"/>
+      <c r="J960" s="8"/>
+      <c r="K960" s="8"/>
     </row>
     <row r="961" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J961" s="9"/>
-      <c r="K961" s="9"/>
+      <c r="J961" s="8"/>
+      <c r="K961" s="8"/>
     </row>
     <row r="962" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J962" s="9"/>
-      <c r="K962" s="9"/>
+      <c r="J962" s="8"/>
+      <c r="K962" s="8"/>
     </row>
     <row r="963" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J963" s="9"/>
-      <c r="K963" s="9"/>
+      <c r="J963" s="8"/>
+      <c r="K963" s="8"/>
     </row>
     <row r="964" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J964" s="9"/>
-      <c r="K964" s="9"/>
+      <c r="J964" s="8"/>
+      <c r="K964" s="8"/>
     </row>
     <row r="965" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J965" s="9"/>
-      <c r="K965" s="9"/>
+      <c r="J965" s="8"/>
+      <c r="K965" s="8"/>
     </row>
     <row r="966" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J966" s="9"/>
-      <c r="K966" s="9"/>
+      <c r="J966" s="8"/>
+      <c r="K966" s="8"/>
     </row>
     <row r="967" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J967" s="9"/>
-      <c r="K967" s="9"/>
+      <c r="J967" s="8"/>
+      <c r="K967" s="8"/>
     </row>
     <row r="968" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J968" s="9"/>
-      <c r="K968" s="9"/>
+      <c r="J968" s="8"/>
+      <c r="K968" s="8"/>
     </row>
     <row r="969" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J969" s="9"/>
-      <c r="K969" s="9"/>
+      <c r="J969" s="8"/>
+      <c r="K969" s="8"/>
     </row>
     <row r="970" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J970" s="9"/>
-      <c r="K970" s="9"/>
+      <c r="J970" s="8"/>
+      <c r="K970" s="8"/>
     </row>
     <row r="971" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J971" s="9"/>
-      <c r="K971" s="9"/>
+      <c r="J971" s="8"/>
+      <c r="K971" s="8"/>
     </row>
     <row r="972" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J972" s="9"/>
-      <c r="K972" s="9"/>
+      <c r="J972" s="8"/>
+      <c r="K972" s="8"/>
     </row>
     <row r="973" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J973" s="9"/>
-      <c r="K973" s="9"/>
+      <c r="J973" s="8"/>
+      <c r="K973" s="8"/>
     </row>
     <row r="974" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J974" s="9"/>
-      <c r="K974" s="9"/>
+      <c r="J974" s="8"/>
+      <c r="K974" s="8"/>
     </row>
     <row r="975" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J975" s="9"/>
-      <c r="K975" s="9"/>
+      <c r="J975" s="8"/>
+      <c r="K975" s="8"/>
     </row>
     <row r="976" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J976" s="9"/>
-      <c r="K976" s="9"/>
+      <c r="J976" s="8"/>
+      <c r="K976" s="8"/>
     </row>
     <row r="977" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J977" s="9"/>
-      <c r="K977" s="9"/>
+      <c r="J977" s="8"/>
+      <c r="K977" s="8"/>
     </row>
     <row r="978" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J978" s="9"/>
-      <c r="K978" s="9"/>
+      <c r="J978" s="8"/>
+      <c r="K978" s="8"/>
     </row>
     <row r="979" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J979" s="9"/>
-      <c r="K979" s="9"/>
+      <c r="J979" s="8"/>
+      <c r="K979" s="8"/>
     </row>
     <row r="980" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J980" s="9"/>
-      <c r="K980" s="9"/>
+      <c r="J980" s="8"/>
+      <c r="K980" s="8"/>
     </row>
     <row r="981" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J981" s="9"/>
-      <c r="K981" s="9"/>
+      <c r="J981" s="8"/>
+      <c r="K981" s="8"/>
     </row>
     <row r="982" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J982" s="9"/>
-      <c r="K982" s="9"/>
+      <c r="J982" s="8"/>
+      <c r="K982" s="8"/>
     </row>
     <row r="983" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J983" s="9"/>
-      <c r="K983" s="9"/>
+      <c r="J983" s="8"/>
+      <c r="K983" s="8"/>
     </row>
     <row r="984" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J984" s="9"/>
-      <c r="K984" s="9"/>
+      <c r="J984" s="8"/>
+      <c r="K984" s="8"/>
     </row>
     <row r="985" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J985" s="9"/>
-      <c r="K985" s="9"/>
+      <c r="J985" s="8"/>
+      <c r="K985" s="8"/>
     </row>
     <row r="986" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J986" s="9"/>
-      <c r="K986" s="9"/>
+      <c r="J986" s="8"/>
+      <c r="K986" s="8"/>
     </row>
     <row r="987" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J987" s="9"/>
-      <c r="K987" s="9"/>
+      <c r="J987" s="8"/>
+      <c r="K987" s="8"/>
     </row>
     <row r="988" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J988" s="9"/>
-      <c r="K988" s="9"/>
+      <c r="J988" s="8"/>
+      <c r="K988" s="8"/>
     </row>
     <row r="989" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J989" s="9"/>
-      <c r="K989" s="9"/>
+      <c r="J989" s="8"/>
+      <c r="K989" s="8"/>
     </row>
     <row r="990" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J990" s="9"/>
-      <c r="K990" s="9"/>
+      <c r="J990" s="8"/>
+      <c r="K990" s="8"/>
     </row>
     <row r="991" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J991" s="9"/>
-      <c r="K991" s="9"/>
+      <c r="J991" s="8"/>
+      <c r="K991" s="8"/>
     </row>
     <row r="992" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J992" s="9"/>
-      <c r="K992" s="9"/>
+      <c r="J992" s="8"/>
+      <c r="K992" s="8"/>
     </row>
     <row r="993" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J993" s="9"/>
-      <c r="K993" s="9"/>
+      <c r="J993" s="8"/>
+      <c r="K993" s="8"/>
     </row>
     <row r="994" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J994" s="9"/>
-      <c r="K994" s="9"/>
+      <c r="J994" s="8"/>
+      <c r="K994" s="8"/>
     </row>
     <row r="995" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J995" s="9"/>
-      <c r="K995" s="9"/>
+      <c r="J995" s="8"/>
+      <c r="K995" s="8"/>
     </row>
     <row r="996" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J996" s="9"/>
-      <c r="K996" s="9"/>
+      <c r="J996" s="8"/>
+      <c r="K996" s="8"/>
     </row>
     <row r="997" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J997" s="9"/>
-      <c r="K997" s="9"/>
+      <c r="J997" s="8"/>
+      <c r="K997" s="8"/>
     </row>
     <row r="998" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J998" s="9"/>
-      <c r="K998" s="9"/>
+      <c r="J998" s="8"/>
+      <c r="K998" s="8"/>
     </row>
     <row r="999" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J999" s="9"/>
-      <c r="K999" s="9"/>
+      <c r="J999" s="8"/>
+      <c r="K999" s="8"/>
     </row>
     <row r="1000" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J1000" s="9"/>
-      <c r="K1000" s="9"/>
+      <c r="J1000" s="8"/>
+      <c r="K1000" s="8"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K438" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K438">
+      <sortCondition ref="A1:A438"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
